--- a/db/MASTER_DATABASE_2026.xlsx
+++ b/db/MASTER_DATABASE_2026.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00 README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Paper" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Machines (Offset)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Digital press rate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Press rates (Offset)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Binding" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Coating &amp; Embellishment" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Hard-case materials rate" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Dieline &amp; converting" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Wire-O diameters" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machines (Offset)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Digital press rate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Press rates (Offset)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binding" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coating &amp; Embellishment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hard-case materials rate" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dieline &amp; converting" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire-O diameters" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -921,7 +921,11 @@
         <v>17.4</v>
       </c>
       <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -952,7 +956,11 @@
         <v>22.3</v>
       </c>
       <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -983,7 +991,11 @@
         <v>19.45</v>
       </c>
       <c r="H7" s="10" t="n"/>
-      <c r="I7" s="10" t="n"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1014,7 +1026,11 @@
         <v>26.75</v>
       </c>
       <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1045,7 +1061,11 @@
         <v>17.9</v>
       </c>
       <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1076,7 +1096,11 @@
         <v>17.9</v>
       </c>
       <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1107,7 +1131,11 @@
         <v>23.9</v>
       </c>
       <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1138,7 +1166,11 @@
         <v>30.2</v>
       </c>
       <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1169,7 +1201,11 @@
         <v>25.05</v>
       </c>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1200,7 +1236,11 @@
         <v>31.75</v>
       </c>
       <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1231,7 +1271,11 @@
         <v>30</v>
       </c>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="10" t="n"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1262,7 +1306,11 @@
         <v>37.95</v>
       </c>
       <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="n"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1293,7 +1341,11 @@
         <v>32</v>
       </c>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1324,7 +1376,11 @@
         <v>29.85</v>
       </c>
       <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1355,7 +1411,11 @@
         <v>41.9</v>
       </c>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1386,7 +1446,11 @@
         <v>36</v>
       </c>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1417,7 +1481,11 @@
         <v>45.55</v>
       </c>
       <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1448,7 +1516,11 @@
         <v>40.3</v>
       </c>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1479,7 +1551,11 @@
         <v>41</v>
       </c>
       <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n"/>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1510,7 +1586,11 @@
         <v>18.96</v>
       </c>
       <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1541,7 +1621,11 @@
         <v>24</v>
       </c>
       <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1572,7 +1656,11 @@
         <v>22.45</v>
       </c>
       <c r="H26" s="10" t="n"/>
-      <c r="I26" s="10" t="n"/>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1603,7 +1691,11 @@
         <v>28.45</v>
       </c>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1634,7 +1726,11 @@
         <v>26</v>
       </c>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1665,7 +1761,11 @@
         <v>32.95</v>
       </c>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -1696,7 +1796,11 @@
         <v>28.75</v>
       </c>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1727,7 +1831,11 @@
         <v>31.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1758,7 +1866,11 @@
         <v>39.85</v>
       </c>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1789,7 +1901,11 @@
         <v>34.55</v>
       </c>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1820,7 +1936,11 @@
         <v>34.56</v>
       </c>
       <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1851,7 +1971,11 @@
         <v>43.7</v>
       </c>
       <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1882,7 +2006,11 @@
         <v>42.8</v>
       </c>
       <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1913,7 +2041,11 @@
         <v>54.2</v>
       </c>
       <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -1944,7 +2076,11 @@
         <v>17.4</v>
       </c>
       <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1975,7 +2111,11 @@
         <v>22.05</v>
       </c>
       <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -2006,7 +2146,11 @@
         <v>22.1</v>
       </c>
       <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -2037,7 +2181,11 @@
         <v>27.95</v>
       </c>
       <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -2068,7 +2216,11 @@
         <v>30.4</v>
       </c>
       <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -2099,7 +2251,11 @@
         <v>38.45</v>
       </c>
       <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2130,7 +2286,11 @@
         <v>28.3</v>
       </c>
       <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -2161,7 +2321,11 @@
         <v>35.85</v>
       </c>
       <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -2192,7 +2356,11 @@
         <v>34.4</v>
       </c>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -2223,7 +2391,11 @@
         <v>43.55</v>
       </c>
       <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -2254,7 +2426,11 @@
         <v>40.05</v>
       </c>
       <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n"/>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -2285,7 +2461,11 @@
         <v>50.65</v>
       </c>
       <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -2316,7 +2496,11 @@
         <v>12.3</v>
       </c>
       <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n"/>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -2347,7 +2531,11 @@
         <v>15.6</v>
       </c>
       <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n"/>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -2378,7 +2566,11 @@
         <v>14.65</v>
       </c>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -2409,7 +2601,11 @@
         <v>17.8</v>
       </c>
       <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: R.J. ENTERPRISE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -2440,7 +2636,11 @@
         <v>25.25</v>
       </c>
       <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -2471,7 +2671,11 @@
         <v>32.25</v>
       </c>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2502,7 +2706,11 @@
         <v>30.5</v>
       </c>
       <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -2533,7 +2741,11 @@
         <v>39</v>
       </c>
       <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2564,7 +2776,11 @@
         <v>35.75</v>
       </c>
       <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -2595,7 +2811,11 @@
         <v>45.75</v>
       </c>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -2626,7 +2846,11 @@
         <v>41.75</v>
       </c>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2657,7 +2881,11 @@
         <v>53.25</v>
       </c>
       <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -2688,7 +2916,11 @@
         <v>50</v>
       </c>
       <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="n"/>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -2719,7 +2951,11 @@
         <v>63.75</v>
       </c>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -2750,7 +2986,11 @@
         <v>58.25</v>
       </c>
       <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -2781,7 +3021,11 @@
         <v>74.25</v>
       </c>
       <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -2812,7 +3056,11 @@
         <v>25.25</v>
       </c>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -2843,7 +3091,11 @@
         <v>32.25</v>
       </c>
       <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -2874,7 +3126,11 @@
         <v>30.5</v>
       </c>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -2905,7 +3161,11 @@
         <v>39</v>
       </c>
       <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -2936,7 +3196,11 @@
         <v>41.75</v>
       </c>
       <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -2967,7 +3231,11 @@
         <v>53.25</v>
       </c>
       <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -2998,7 +3266,11 @@
         <v>58.25</v>
       </c>
       <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -3029,7 +3301,11 @@
         <v>74.25</v>
       </c>
       <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -3060,7 +3336,11 @@
         <v>18.5</v>
       </c>
       <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -3091,7 +3371,11 @@
         <v>22</v>
       </c>
       <c r="H75" s="10" t="n"/>
-      <c r="I75" s="10" t="n"/>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -3122,7 +3406,11 @@
         <v>23</v>
       </c>
       <c r="H76" s="10" t="n"/>
-      <c r="I76" s="10" t="n"/>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -3153,7 +3441,11 @@
         <v>22.75</v>
       </c>
       <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -3184,7 +3476,11 @@
         <v>27.25</v>
       </c>
       <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -3215,7 +3511,11 @@
         <v>28.75</v>
       </c>
       <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -3246,7 +3546,11 @@
         <v>28</v>
       </c>
       <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -3277,7 +3581,11 @@
         <v>33.75</v>
       </c>
       <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -3308,7 +3616,11 @@
         <v>35.25</v>
       </c>
       <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -3339,7 +3651,11 @@
         <v>33.25</v>
       </c>
       <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -3370,7 +3686,11 @@
         <v>40</v>
       </c>
       <c r="H84" s="10" t="n"/>
-      <c r="I84" s="10" t="n"/>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -3401,7 +3721,11 @@
         <v>42</v>
       </c>
       <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -3432,7 +3756,11 @@
         <v>42</v>
       </c>
       <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -3463,7 +3791,11 @@
         <v>50.25</v>
       </c>
       <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -3494,7 +3826,11 @@
         <v>52.75</v>
       </c>
       <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -3525,7 +3861,11 @@
         <v>47.25</v>
       </c>
       <c r="H89" s="10" t="n"/>
-      <c r="I89" s="10" t="n"/>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -3556,7 +3896,11 @@
         <v>56.75</v>
       </c>
       <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -3587,7 +3931,11 @@
         <v>59.5</v>
       </c>
       <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -3618,7 +3966,11 @@
         <v>38</v>
       </c>
       <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -3649,7 +4001,11 @@
         <v>40</v>
       </c>
       <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -3680,7 +4036,11 @@
         <v>50.5</v>
       </c>
       <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -3711,7 +4071,11 @@
         <v>61.5</v>
       </c>
       <c r="H95" s="10" t="n"/>
-      <c r="I95" s="10" t="n"/>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -3742,7 +4106,11 @@
         <v>58.25</v>
       </c>
       <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -3773,7 +4141,11 @@
         <v>73.5</v>
       </c>
       <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -3804,7 +4176,11 @@
         <v>72.75</v>
       </c>
       <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="n"/>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -3835,7 +4211,11 @@
         <v>92</v>
       </c>
       <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -3866,7 +4246,11 @@
         <v>38</v>
       </c>
       <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -3897,7 +4281,11 @@
         <v>40</v>
       </c>
       <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="n"/>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -3928,7 +4316,11 @@
         <v>50.5</v>
       </c>
       <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -3959,7 +4351,11 @@
         <v>61.5</v>
       </c>
       <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -3990,7 +4386,11 @@
         <v>63.25</v>
       </c>
       <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -4021,7 +4421,11 @@
         <v>79.75</v>
       </c>
       <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -4052,7 +4456,11 @@
         <v>72.75</v>
       </c>
       <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -4083,7 +4491,11 @@
         <v>92</v>
       </c>
       <c r="H107" s="10" t="n"/>
-      <c r="I107" s="10" t="n"/>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -4114,7 +4526,11 @@
         <v>51</v>
       </c>
       <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -4145,7 +4561,11 @@
         <v>51</v>
       </c>
       <c r="H109" s="10" t="n"/>
-      <c r="I109" s="10" t="n"/>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -4176,7 +4596,11 @@
         <v>54</v>
       </c>
       <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -4207,7 +4631,11 @@
         <v>51</v>
       </c>
       <c r="H111" s="10" t="n"/>
-      <c r="I111" s="10" t="n"/>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -4238,7 +4666,11 @@
         <v>54</v>
       </c>
       <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -4269,7 +4701,11 @@
         <v>51</v>
       </c>
       <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -4300,7 +4736,11 @@
         <v>43</v>
       </c>
       <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -4331,7 +4771,11 @@
         <v>43</v>
       </c>
       <c r="H115" s="10" t="n"/>
-      <c r="I115" s="10" t="n"/>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -4362,7 +4806,11 @@
         <v>51</v>
       </c>
       <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -4393,7 +4841,11 @@
         <v>41</v>
       </c>
       <c r="H117" s="10" t="n"/>
-      <c r="I117" s="10" t="n"/>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -4424,7 +4876,11 @@
         <v>21</v>
       </c>
       <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="n"/>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -4455,7 +4911,11 @@
         <v>43.5</v>
       </c>
       <c r="H119" s="10" t="n"/>
-      <c r="I119" s="10" t="n"/>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -4486,7 +4946,11 @@
         <v>21</v>
       </c>
       <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
@@ -4517,7 +4981,11 @@
         <v>31</v>
       </c>
       <c r="H121" s="10" t="n"/>
-      <c r="I121" s="10" t="n"/>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -4548,7 +5016,11 @@
         <v>43.5</v>
       </c>
       <c r="H122" s="10" t="n"/>
-      <c r="I122" s="10" t="n"/>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -4579,7 +5051,11 @@
         <v>12.75</v>
       </c>
       <c r="H123" s="10" t="n"/>
-      <c r="I123" s="10" t="n"/>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
@@ -4610,7 +5086,11 @@
         <v>16</v>
       </c>
       <c r="H124" s="10" t="n"/>
-      <c r="I124" s="10" t="n"/>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -4641,7 +5121,11 @@
         <v>14.5</v>
       </c>
       <c r="H125" s="10" t="n"/>
-      <c r="I125" s="10" t="n"/>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -4672,7 +5156,11 @@
         <v>18.25</v>
       </c>
       <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="n"/>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -4703,7 +5191,11 @@
         <v>17.75</v>
       </c>
       <c r="H127" s="10" t="n"/>
-      <c r="I127" s="10" t="n"/>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
@@ -4734,7 +5226,11 @@
         <v>22.5</v>
       </c>
       <c r="H128" s="10" t="n"/>
-      <c r="I128" s="10" t="n"/>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -4765,7 +5261,11 @@
         <v>21</v>
       </c>
       <c r="H129" s="10" t="n"/>
-      <c r="I129" s="10" t="n"/>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
@@ -4796,7 +5296,11 @@
         <v>26.5</v>
       </c>
       <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="n"/>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -4827,7 +5331,11 @@
         <v>28.75</v>
       </c>
       <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="n"/>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
@@ -4858,7 +5366,11 @@
         <v>36.25</v>
       </c>
       <c r="H132" s="10" t="n"/>
-      <c r="I132" s="10" t="n"/>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -4889,7 +5401,11 @@
         <v>33.75</v>
       </c>
       <c r="H133" s="10" t="n"/>
-      <c r="I133" s="10" t="n"/>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
@@ -4920,7 +5436,11 @@
         <v>42.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
@@ -4951,7 +5471,11 @@
         <v>142</v>
       </c>
       <c r="H135" s="10" t="n"/>
-      <c r="I135" s="10" t="n"/>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
@@ -4982,7 +5506,11 @@
         <v>243.5</v>
       </c>
       <c r="H136" s="10" t="n"/>
-      <c r="I136" s="10" t="n"/>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
@@ -5013,7 +5541,11 @@
         <v>380</v>
       </c>
       <c r="H137" s="10" t="n"/>
-      <c r="I137" s="10" t="n"/>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
@@ -5044,7 +5576,11 @@
         <v>15</v>
       </c>
       <c r="H138" s="10" t="n"/>
-      <c r="I138" s="10" t="n"/>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -5075,7 +5611,11 @@
         <v>22.5</v>
       </c>
       <c r="H139" s="10" t="n"/>
-      <c r="I139" s="10" t="n"/>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
@@ -5106,7 +5646,11 @@
         <v>19.5</v>
       </c>
       <c r="H140" s="10" t="n"/>
-      <c r="I140" s="10" t="n"/>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
@@ -5137,7 +5681,11 @@
         <v>28.75</v>
       </c>
       <c r="H141" s="10" t="n"/>
-      <c r="I141" s="10" t="n"/>
+      <c r="I141" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
@@ -5168,7 +5716,11 @@
         <v>40.5</v>
       </c>
       <c r="H142" s="10" t="n"/>
-      <c r="I142" s="10" t="n"/>
+      <c r="I142" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -5199,7 +5751,11 @@
         <v>48.5</v>
       </c>
       <c r="H143" s="10" t="n"/>
-      <c r="I143" s="10" t="n"/>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
@@ -5230,7 +5786,11 @@
         <v>88</v>
       </c>
       <c r="H144" s="10" t="n"/>
-      <c r="I144" s="10" t="n"/>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -5261,7 +5821,11 @@
         <v>104</v>
       </c>
       <c r="H145" s="10" t="n"/>
-      <c r="I145" s="10" t="n"/>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
@@ -5292,7 +5856,11 @@
         <v>138</v>
       </c>
       <c r="H146" s="10" t="n"/>
-      <c r="I146" s="10" t="n"/>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
@@ -5323,7 +5891,11 @@
         <v>157</v>
       </c>
       <c r="H147" s="10" t="n"/>
-      <c r="I147" s="10" t="n"/>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
@@ -5354,7 +5926,11 @@
         <v>327</v>
       </c>
       <c r="H148" s="10" t="n"/>
-      <c r="I148" s="10" t="n"/>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
@@ -5385,7 +5961,11 @@
         <v>95</v>
       </c>
       <c r="H149" s="10" t="n"/>
-      <c r="I149" s="10" t="n"/>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: SONAFINE CORPORATION LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
@@ -5416,7 +5996,11 @@
         <v>4.03</v>
       </c>
       <c r="H150" s="10" t="n"/>
-      <c r="I150" s="10" t="n"/>
+      <c r="I150" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
@@ -5447,7 +6031,11 @@
         <v>5.56</v>
       </c>
       <c r="H151" s="10" t="n"/>
-      <c r="I151" s="10" t="n"/>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
@@ -5478,7 +6066,11 @@
         <v>6.05</v>
       </c>
       <c r="H152" s="10" t="n"/>
-      <c r="I152" s="10" t="n"/>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -5509,7 +6101,11 @@
         <v>4.43</v>
       </c>
       <c r="H153" s="10" t="n"/>
-      <c r="I153" s="10" t="n"/>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
@@ -5540,7 +6136,11 @@
         <v>6.11</v>
       </c>
       <c r="H154" s="10" t="n"/>
-      <c r="I154" s="10" t="n"/>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
@@ -5571,7 +6171,11 @@
         <v>6.64</v>
       </c>
       <c r="H155" s="10" t="n"/>
-      <c r="I155" s="10" t="n"/>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -5602,7 +6206,11 @@
         <v>6.48</v>
       </c>
       <c r="H156" s="10" t="n"/>
-      <c r="I156" s="10" t="n"/>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
@@ -5633,7 +6241,11 @@
         <v>4.92</v>
       </c>
       <c r="H157" s="10" t="n"/>
-      <c r="I157" s="10" t="n"/>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
@@ -5664,7 +6276,11 @@
         <v>6.79</v>
       </c>
       <c r="H158" s="10" t="n"/>
-      <c r="I158" s="10" t="n"/>
+      <c r="I158" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
@@ -5695,7 +6311,11 @@
         <v>5.77</v>
       </c>
       <c r="H159" s="10" t="n"/>
-      <c r="I159" s="10" t="n"/>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
@@ -5726,7 +6346,11 @@
         <v>8.859999999999999</v>
       </c>
       <c r="H160" s="10" t="n"/>
-      <c r="I160" s="10" t="n"/>
+      <c r="I160" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
@@ -5757,7 +6381,11 @@
         <v>8.15</v>
       </c>
       <c r="H161" s="10" t="n"/>
-      <c r="I161" s="10" t="n"/>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="8" t="inlineStr">
@@ -5788,7 +6416,11 @@
         <v>5.9</v>
       </c>
       <c r="H162" s="10" t="n"/>
-      <c r="I162" s="10" t="n"/>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
@@ -5819,7 +6451,11 @@
         <v>6.4</v>
       </c>
       <c r="H163" s="10" t="n"/>
-      <c r="I163" s="10" t="n"/>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
@@ -5850,7 +6486,11 @@
         <v>8.83</v>
       </c>
       <c r="H164" s="10" t="n"/>
-      <c r="I164" s="10" t="n"/>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
@@ -5881,7 +6521,11 @@
         <v>9.59</v>
       </c>
       <c r="H165" s="10" t="n"/>
-      <c r="I165" s="10" t="n"/>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
@@ -5912,7 +6556,11 @@
         <v>7.5</v>
       </c>
       <c r="H166" s="10" t="n"/>
-      <c r="I166" s="10" t="n"/>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -5943,7 +6591,11 @@
         <v>9.59</v>
       </c>
       <c r="H167" s="10" t="n"/>
-      <c r="I167" s="10" t="n"/>
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
@@ -5974,7 +6626,11 @@
         <v>8.83</v>
       </c>
       <c r="H168" s="10" t="n"/>
-      <c r="I168" s="10" t="n"/>
+      <c r="I168" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
@@ -6005,7 +6661,11 @@
         <v>7.72</v>
       </c>
       <c r="H169" s="10" t="n"/>
-      <c r="I169" s="10" t="n"/>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
@@ -6036,7 +6696,11 @@
         <v>10.66</v>
       </c>
       <c r="H170" s="10" t="n"/>
-      <c r="I170" s="10" t="n"/>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
@@ -6067,7 +6731,11 @@
         <v>11.59</v>
       </c>
       <c r="H171" s="10" t="n"/>
-      <c r="I171" s="10" t="n"/>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
@@ -6098,7 +6766,11 @@
         <v>12.09</v>
       </c>
       <c r="H172" s="10" t="n"/>
-      <c r="I172" s="10" t="n"/>
+      <c r="I172" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
@@ -6129,7 +6801,11 @@
         <v>11.12</v>
       </c>
       <c r="H173" s="10" t="n"/>
-      <c r="I173" s="10" t="n"/>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
@@ -6160,7 +6836,11 @@
         <v>8.06</v>
       </c>
       <c r="H174" s="10" t="n"/>
-      <c r="I174" s="10" t="n"/>
+      <c r="I174" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
@@ -6191,7 +6871,11 @@
         <v>8.06</v>
       </c>
       <c r="H175" s="10" t="n"/>
-      <c r="I175" s="10" t="n"/>
+      <c r="I175" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="8" t="inlineStr">
@@ -6222,7 +6906,11 @@
         <v>12.09</v>
       </c>
       <c r="H176" s="10" t="n"/>
-      <c r="I176" s="10" t="n"/>
+      <c r="I176" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
@@ -6253,7 +6941,11 @@
         <v>9.48</v>
       </c>
       <c r="H177" s="10" t="n"/>
-      <c r="I177" s="10" t="n"/>
+      <c r="I177" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
@@ -6284,7 +6976,11 @@
         <v>13.08</v>
       </c>
       <c r="H178" s="10" t="n"/>
-      <c r="I178" s="10" t="n"/>
+      <c r="I178" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
@@ -6315,7 +7011,11 @@
         <v>14.22</v>
       </c>
       <c r="H179" s="10" t="n"/>
-      <c r="I179" s="10" t="n"/>
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
@@ -6346,7 +7046,11 @@
         <v>10.22</v>
       </c>
       <c r="H180" s="10" t="n"/>
-      <c r="I180" s="10" t="n"/>
+      <c r="I180" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
@@ -6377,7 +7081,11 @@
         <v>14.93</v>
       </c>
       <c r="H181" s="10" t="n"/>
-      <c r="I181" s="10" t="n"/>
+      <c r="I181" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
@@ -6408,7 +7116,11 @@
         <v>9.949999999999999</v>
       </c>
       <c r="H182" s="10" t="n"/>
-      <c r="I182" s="10" t="n"/>
+      <c r="I182" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
@@ -6439,7 +7151,11 @@
         <v>10.22</v>
       </c>
       <c r="H183" s="10" t="n"/>
-      <c r="I183" s="10" t="n"/>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="8" t="inlineStr">
@@ -6470,7 +7186,11 @@
         <v>13.74</v>
       </c>
       <c r="H184" s="10" t="n"/>
-      <c r="I184" s="10" t="n"/>
+      <c r="I184" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
@@ -6501,7 +7221,11 @@
         <v>14.93</v>
       </c>
       <c r="H185" s="10" t="n"/>
-      <c r="I185" s="10" t="n"/>
+      <c r="I185" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="8" t="inlineStr">
@@ -6532,7 +7256,11 @@
         <v>17.77</v>
       </c>
       <c r="H186" s="10" t="n"/>
-      <c r="I186" s="10" t="n"/>
+      <c r="I186" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
@@ -6563,7 +7291,11 @@
         <v>16.35</v>
       </c>
       <c r="H187" s="10" t="n"/>
-      <c r="I187" s="10" t="n"/>
+      <c r="I187" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="8" t="inlineStr">
@@ -6594,7 +7326,11 @@
         <v>11.85</v>
       </c>
       <c r="H188" s="10" t="n"/>
-      <c r="I188" s="10" t="n"/>
+      <c r="I188" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
@@ -6625,7 +7361,11 @@
         <v>12.17</v>
       </c>
       <c r="H189" s="10" t="n"/>
-      <c r="I189" s="10" t="n"/>
+      <c r="I189" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
@@ -6656,7 +7396,11 @@
         <v>21.33</v>
       </c>
       <c r="H190" s="10" t="n"/>
-      <c r="I190" s="10" t="n"/>
+      <c r="I190" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
@@ -6687,7 +7431,11 @@
         <v>19.62</v>
       </c>
       <c r="H191" s="10" t="n"/>
-      <c r="I191" s="10" t="n"/>
+      <c r="I191" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="8" t="inlineStr">
@@ -6718,7 +7466,11 @@
         <v>14.22</v>
       </c>
       <c r="H192" s="10" t="n"/>
-      <c r="I192" s="10" t="n"/>
+      <c r="I192" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
@@ -6749,7 +7501,11 @@
         <v>18.68</v>
       </c>
       <c r="H193" s="10" t="n"/>
-      <c r="I193" s="10" t="n"/>
+      <c r="I193" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="8" t="inlineStr">
@@ -6780,7 +7536,11 @@
         <v>17.18</v>
       </c>
       <c r="H194" s="10" t="n"/>
-      <c r="I194" s="10" t="n"/>
+      <c r="I194" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
@@ -6811,7 +7571,11 @@
         <v>12.78</v>
       </c>
       <c r="H195" s="10" t="n"/>
-      <c r="I195" s="10" t="n"/>
+      <c r="I195" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="8" t="inlineStr">
@@ -6842,7 +7606,11 @@
         <v>22.41</v>
       </c>
       <c r="H196" s="10" t="n"/>
-      <c r="I196" s="10" t="n"/>
+      <c r="I196" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
@@ -6873,7 +7641,11 @@
         <v>20.62</v>
       </c>
       <c r="H197" s="10" t="n"/>
-      <c r="I197" s="10" t="n"/>
+      <c r="I197" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="8" t="inlineStr">
@@ -6904,7 +7676,11 @@
         <v>15.34</v>
       </c>
       <c r="H198" s="10" t="n"/>
-      <c r="I198" s="10" t="n"/>
+      <c r="I198" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="8" t="inlineStr">
@@ -6935,7 +7711,11 @@
         <v>26.14</v>
       </c>
       <c r="H199" s="10" t="n"/>
-      <c r="I199" s="10" t="n"/>
+      <c r="I199" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="8" t="inlineStr">
@@ -6966,7 +7746,11 @@
         <v>24.05</v>
       </c>
       <c r="H200" s="10" t="n"/>
-      <c r="I200" s="10" t="n"/>
+      <c r="I200" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="8" t="inlineStr">
@@ -6997,7 +7781,11 @@
         <v>17.89</v>
       </c>
       <c r="H201" s="10" t="n"/>
-      <c r="I201" s="10" t="n"/>
+      <c r="I201" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="8" t="inlineStr">
@@ -7028,7 +7816,11 @@
         <v>11.86</v>
       </c>
       <c r="H202" s="10" t="n"/>
-      <c r="I202" s="10" t="n"/>
+      <c r="I202" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="8" t="inlineStr">
@@ -7059,7 +7851,11 @@
         <v>15.94</v>
       </c>
       <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
+      <c r="I203" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="8" t="inlineStr">
@@ -7090,7 +7886,11 @@
         <v>18.29</v>
       </c>
       <c r="H204" s="10" t="n"/>
-      <c r="I204" s="10" t="n"/>
+      <c r="I204" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="8" t="inlineStr">
@@ -7121,7 +7921,11 @@
         <v>25.16</v>
       </c>
       <c r="H205" s="10" t="n"/>
-      <c r="I205" s="10" t="n"/>
+      <c r="I205" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="8" t="inlineStr">
@@ -7152,7 +7956,11 @@
         <v>13.28</v>
       </c>
       <c r="H206" s="10" t="n"/>
-      <c r="I206" s="10" t="n"/>
+      <c r="I206" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="8" t="inlineStr">
@@ -7183,7 +7991,11 @@
         <v>17.85</v>
       </c>
       <c r="H207" s="10" t="n"/>
-      <c r="I207" s="10" t="n"/>
+      <c r="I207" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="8" t="inlineStr">
@@ -7214,7 +8026,11 @@
         <v>20.48</v>
       </c>
       <c r="H208" s="10" t="n"/>
-      <c r="I208" s="10" t="n"/>
+      <c r="I208" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
@@ -7245,7 +8061,11 @@
         <v>28.18</v>
       </c>
       <c r="H209" s="10" t="n"/>
-      <c r="I209" s="10" t="n"/>
+      <c r="I209" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="8" t="inlineStr">
@@ -7276,7 +8096,11 @@
         <v>14.23</v>
       </c>
       <c r="H210" s="10" t="n"/>
-      <c r="I210" s="10" t="n"/>
+      <c r="I210" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="8" t="inlineStr">
@@ -7307,7 +8131,11 @@
         <v>19.13</v>
       </c>
       <c r="H211" s="10" t="n"/>
-      <c r="I211" s="10" t="n"/>
+      <c r="I211" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="8" t="inlineStr">
@@ -7338,7 +8166,11 @@
         <v>21.95</v>
       </c>
       <c r="H212" s="10" t="n"/>
-      <c r="I212" s="10" t="n"/>
+      <c r="I212" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="8" t="inlineStr">
@@ -7369,7 +8201,11 @@
         <v>30.2</v>
       </c>
       <c r="H213" s="10" t="n"/>
-      <c r="I213" s="10" t="n"/>
+      <c r="I213" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="8" t="inlineStr">
@@ -7400,7 +8236,11 @@
         <v>3.19</v>
       </c>
       <c r="H214" s="10" t="n"/>
-      <c r="I214" s="10" t="n"/>
+      <c r="I214" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="8" t="inlineStr">
@@ -7431,7 +8271,11 @@
         <v>4.79</v>
       </c>
       <c r="H215" s="10" t="n"/>
-      <c r="I215" s="10" t="n"/>
+      <c r="I215" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="8" t="inlineStr">
@@ -7462,7 +8306,11 @@
         <v>4.4</v>
       </c>
       <c r="H216" s="10" t="n"/>
-      <c r="I216" s="10" t="n"/>
+      <c r="I216" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="8" t="inlineStr">
@@ -7493,7 +8341,11 @@
         <v>3.74</v>
       </c>
       <c r="H217" s="10" t="n"/>
-      <c r="I217" s="10" t="n"/>
+      <c r="I217" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="8" t="inlineStr">
@@ -7524,7 +8376,11 @@
         <v>5.62</v>
       </c>
       <c r="H218" s="10" t="n"/>
-      <c r="I218" s="10" t="n"/>
+      <c r="I218" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="8" t="inlineStr">
@@ -7555,7 +8411,11 @@
         <v>5.17</v>
       </c>
       <c r="H219" s="10" t="n"/>
-      <c r="I219" s="10" t="n"/>
+      <c r="I219" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="8" t="inlineStr">
@@ -7586,7 +8446,11 @@
         <v>4.21</v>
       </c>
       <c r="H220" s="10" t="n"/>
-      <c r="I220" s="10" t="n"/>
+      <c r="I220" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="8" t="inlineStr">
@@ -7617,7 +8481,11 @@
         <v>6.32</v>
       </c>
       <c r="H221" s="10" t="n"/>
-      <c r="I221" s="10" t="n"/>
+      <c r="I221" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="8" t="inlineStr">
@@ -7648,7 +8516,11 @@
         <v>5.81</v>
       </c>
       <c r="H222" s="10" t="n"/>
-      <c r="I222" s="10" t="n"/>
+      <c r="I222" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
@@ -7679,7 +8551,11 @@
         <v>4.68</v>
       </c>
       <c r="H223" s="10" t="n"/>
-      <c r="I223" s="10" t="n"/>
+      <c r="I223" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="8" t="inlineStr">
@@ -7710,7 +8586,11 @@
         <v>5.62</v>
       </c>
       <c r="H224" s="10" t="n"/>
-      <c r="I224" s="10" t="n"/>
+      <c r="I224" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="8" t="inlineStr">
@@ -7741,7 +8621,11 @@
         <v>7.75</v>
       </c>
       <c r="H225" s="10" t="n"/>
-      <c r="I225" s="10" t="n"/>
+      <c r="I225" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="8" t="inlineStr">
@@ -7772,7 +8656,11 @@
         <v>8.42</v>
       </c>
       <c r="H226" s="10" t="n"/>
-      <c r="I226" s="10" t="n"/>
+      <c r="I226" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
@@ -7803,7 +8691,11 @@
         <v>2.7</v>
       </c>
       <c r="H227" s="10" t="n"/>
-      <c r="I227" s="10" t="n"/>
+      <c r="I227" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
@@ -7834,7 +8726,11 @@
         <v>3.73</v>
       </c>
       <c r="H228" s="10" t="n"/>
-      <c r="I228" s="10" t="n"/>
+      <c r="I228" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="8" t="inlineStr">
@@ -7865,7 +8761,11 @@
         <v>4.05</v>
       </c>
       <c r="H229" s="10" t="n"/>
-      <c r="I229" s="10" t="n"/>
+      <c r="I229" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="8" t="inlineStr">
@@ -7896,7 +8796,11 @@
         <v>3.15</v>
       </c>
       <c r="H230" s="10" t="n"/>
-      <c r="I230" s="10" t="n"/>
+      <c r="I230" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="8" t="inlineStr">
@@ -7927,7 +8831,11 @@
         <v>4.35</v>
       </c>
       <c r="H231" s="10" t="n"/>
-      <c r="I231" s="10" t="n"/>
+      <c r="I231" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="8" t="inlineStr">
@@ -7958,7 +8866,11 @@
         <v>4.72</v>
       </c>
       <c r="H232" s="10" t="n"/>
-      <c r="I232" s="10" t="n"/>
+      <c r="I232" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="8" t="inlineStr">
@@ -7989,7 +8901,11 @@
         <v>3.6</v>
       </c>
       <c r="H233" s="10" t="n"/>
-      <c r="I233" s="10" t="n"/>
+      <c r="I233" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="8" t="inlineStr">
@@ -8020,7 +8936,11 @@
         <v>4.97</v>
       </c>
       <c r="H234" s="10" t="n"/>
-      <c r="I234" s="10" t="n"/>
+      <c r="I234" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="8" t="inlineStr">
@@ -8051,7 +8971,11 @@
         <v>5.4</v>
       </c>
       <c r="H235" s="10" t="n"/>
-      <c r="I235" s="10" t="n"/>
+      <c r="I235" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="8" t="inlineStr">
@@ -8082,7 +9006,11 @@
         <v>4.05</v>
       </c>
       <c r="H236" s="10" t="n"/>
-      <c r="I236" s="10" t="n"/>
+      <c r="I236" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="8" t="inlineStr">
@@ -8113,7 +9041,11 @@
         <v>5.59</v>
       </c>
       <c r="H237" s="10" t="n"/>
-      <c r="I237" s="10" t="n"/>
+      <c r="I237" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="8" t="inlineStr">
@@ -8144,7 +9076,11 @@
         <v>6.08</v>
       </c>
       <c r="H238" s="10" t="n"/>
-      <c r="I238" s="10" t="n"/>
+      <c r="I238" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="8" t="inlineStr">
@@ -8175,7 +9111,11 @@
         <v>5.4</v>
       </c>
       <c r="H239" s="10" t="n"/>
-      <c r="I239" s="10" t="n"/>
+      <c r="I239" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="8" t="inlineStr">
@@ -8206,7 +9146,11 @@
         <v>7.45</v>
       </c>
       <c r="H240" s="10" t="n"/>
-      <c r="I240" s="10" t="n"/>
+      <c r="I240" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="8" t="inlineStr">
@@ -8237,7 +9181,11 @@
         <v>8.1</v>
       </c>
       <c r="H241" s="10" t="n"/>
-      <c r="I241" s="10" t="n"/>
+      <c r="I241" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="8" t="inlineStr">
@@ -8268,7 +9216,11 @@
         <v>13.45</v>
       </c>
       <c r="H242" s="10" t="n"/>
-      <c r="I242" s="10" t="n"/>
+      <c r="I242" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="8" t="inlineStr">
@@ -8299,7 +9251,11 @@
         <v>18.08</v>
       </c>
       <c r="H243" s="10" t="n"/>
-      <c r="I243" s="10" t="n"/>
+      <c r="I243" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="8" t="inlineStr">
@@ -8330,7 +9286,11 @@
         <v>20.75</v>
       </c>
       <c r="H244" s="10" t="n"/>
-      <c r="I244" s="10" t="n"/>
+      <c r="I244" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="8" t="inlineStr">
@@ -8361,7 +9321,11 @@
         <v>28.55</v>
       </c>
       <c r="H245" s="10" t="n"/>
-      <c r="I245" s="10" t="n"/>
+      <c r="I245" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="8" t="inlineStr">
@@ -8392,7 +9356,11 @@
         <v>14.41</v>
       </c>
       <c r="H246" s="10" t="n"/>
-      <c r="I246" s="10" t="n"/>
+      <c r="I246" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="8" t="inlineStr">
@@ -8423,7 +9391,11 @@
         <v>19.38</v>
       </c>
       <c r="H247" s="10" t="n"/>
-      <c r="I247" s="10" t="n"/>
+      <c r="I247" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="8" t="inlineStr">
@@ -8454,7 +9426,11 @@
         <v>22.23</v>
       </c>
       <c r="H248" s="10" t="n"/>
-      <c r="I248" s="10" t="n"/>
+      <c r="I248" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="8" t="inlineStr">
@@ -8485,7 +9461,11 @@
         <v>30.59</v>
       </c>
       <c r="H249" s="10" t="n"/>
-      <c r="I249" s="10" t="n"/>
+      <c r="I249" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="8" t="inlineStr">
@@ -8516,7 +9496,11 @@
         <v>22.6</v>
       </c>
       <c r="H250" s="10" t="n"/>
-      <c r="I250" s="10" t="n"/>
+      <c r="I250" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="8" t="inlineStr">
@@ -8547,7 +9531,11 @@
         <v>35.69</v>
       </c>
       <c r="H251" s="10" t="n"/>
-      <c r="I251" s="10" t="n"/>
+      <c r="I251" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="8" t="inlineStr">
@@ -8578,7 +9566,11 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H252" s="10" t="n"/>
-      <c r="I252" s="10" t="n"/>
+      <c r="I252" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="8" t="inlineStr">
@@ -8609,7 +9601,11 @@
         <v>4.08</v>
       </c>
       <c r="H253" s="10" t="n"/>
-      <c r="I253" s="10" t="n"/>
+      <c r="I253" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="8" t="inlineStr">
@@ -8640,7 +9636,11 @@
         <v>5.63</v>
       </c>
       <c r="H254" s="10" t="n"/>
-      <c r="I254" s="10" t="n"/>
+      <c r="I254" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="8" t="inlineStr">
@@ -8671,7 +9671,11 @@
         <v>6.12</v>
       </c>
       <c r="H255" s="10" t="n"/>
-      <c r="I255" s="10" t="n"/>
+      <c r="I255" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="8" t="inlineStr">
@@ -8701,8 +9705,14 @@
       <c r="G256" s="9" t="n">
         <v>4.48</v>
       </c>
-      <c r="H256" s="10" t="n"/>
-      <c r="I256" s="10" t="n"/>
+      <c r="H256" s="10" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="I256" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day · source Rs 4.428 vs current 4.48</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="8" t="inlineStr">
@@ -8732,8 +9742,14 @@
       <c r="G257" s="9" t="n">
         <v>6.19</v>
       </c>
-      <c r="H257" s="10" t="n"/>
-      <c r="I257" s="10" t="n"/>
+      <c r="H257" s="10" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="I257" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day · source Rs 6.111 vs current 6.19</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="8" t="inlineStr">
@@ -8763,8 +9779,14 @@
       <c r="G258" s="9" t="n">
         <v>6.72</v>
       </c>
-      <c r="H258" s="10" t="n"/>
-      <c r="I258" s="10" t="n"/>
+      <c r="H258" s="10" t="n">
+        <v>6.642</v>
+      </c>
+      <c r="I258" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day · source Rs 6.642 vs current 6.72</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="8" t="inlineStr">
@@ -8795,7 +9817,11 @@
         <v>4.8</v>
       </c>
       <c r="H259" s="10" t="n"/>
-      <c r="I259" s="10" t="n"/>
+      <c r="I259" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="8" t="inlineStr">
@@ -8826,7 +9852,11 @@
         <v>6.62</v>
       </c>
       <c r="H260" s="10" t="n"/>
-      <c r="I260" s="10" t="n"/>
+      <c r="I260" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="8" t="inlineStr">
@@ -8857,7 +9887,11 @@
         <v>5.63</v>
       </c>
       <c r="H261" s="10" t="n"/>
-      <c r="I261" s="10" t="n"/>
+      <c r="I261" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="8" t="inlineStr">
@@ -8888,7 +9922,11 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H262" s="10" t="n"/>
-      <c r="I262" s="10" t="n"/>
+      <c r="I262" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="8" t="inlineStr">
@@ -8919,7 +9957,11 @@
         <v>7.95</v>
       </c>
       <c r="H263" s="10" t="n"/>
-      <c r="I263" s="10" t="n"/>
+      <c r="I263" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="8" t="inlineStr">
@@ -8950,7 +9992,11 @@
         <v>5.76</v>
       </c>
       <c r="H264" s="10" t="n"/>
-      <c r="I264" s="10" t="n"/>
+      <c r="I264" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="8" t="inlineStr">
@@ -8981,7 +10027,11 @@
         <v>6.24</v>
       </c>
       <c r="H265" s="10" t="n"/>
-      <c r="I265" s="10" t="n"/>
+      <c r="I265" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="8" t="inlineStr">
@@ -9012,7 +10062,11 @@
         <v>8.609999999999999</v>
       </c>
       <c r="H266" s="10" t="n"/>
-      <c r="I266" s="10" t="n"/>
+      <c r="I266" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="8" t="inlineStr">
@@ -9043,7 +10097,11 @@
         <v>9.359999999999999</v>
       </c>
       <c r="H267" s="10" t="n"/>
-      <c r="I267" s="10" t="n"/>
+      <c r="I267" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="8" t="inlineStr">
@@ -9074,7 +10132,11 @@
         <v>7.32</v>
       </c>
       <c r="H268" s="10" t="n"/>
-      <c r="I268" s="10" t="n"/>
+      <c r="I268" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="8" t="inlineStr">
@@ -9105,7 +10167,11 @@
         <v>7.54</v>
       </c>
       <c r="H269" s="10" t="n"/>
-      <c r="I269" s="10" t="n"/>
+      <c r="I269" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="8" t="inlineStr">
@@ -9136,7 +10202,11 @@
         <v>10.4</v>
       </c>
       <c r="H270" s="10" t="n"/>
-      <c r="I270" s="10" t="n"/>
+      <c r="I270" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="8" t="inlineStr">
@@ -9167,7 +10237,11 @@
         <v>11.3</v>
       </c>
       <c r="H271" s="10" t="n"/>
-      <c r="I271" s="10" t="n"/>
+      <c r="I271" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="8" t="inlineStr">
@@ -9198,7 +10272,11 @@
         <v>12.24</v>
       </c>
       <c r="H272" s="10" t="n"/>
-      <c r="I272" s="10" t="n"/>
+      <c r="I272" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="8" t="inlineStr">
@@ -9229,7 +10307,11 @@
         <v>11.26</v>
       </c>
       <c r="H273" s="10" t="n"/>
-      <c r="I273" s="10" t="n"/>
+      <c r="I273" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="8" t="inlineStr">
@@ -9260,7 +10342,11 @@
         <v>8.16</v>
       </c>
       <c r="H274" s="10" t="n"/>
-      <c r="I274" s="10" t="n"/>
+      <c r="I274" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="8" t="inlineStr">
@@ -9291,7 +10377,11 @@
         <v>9.119999999999999</v>
       </c>
       <c r="H275" s="10" t="n"/>
-      <c r="I275" s="10" t="n"/>
+      <c r="I275" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="8" t="inlineStr">
@@ -9322,7 +10412,11 @@
         <v>12.59</v>
       </c>
       <c r="H276" s="10" t="n"/>
-      <c r="I276" s="10" t="n"/>
+      <c r="I276" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="8" t="inlineStr">
@@ -9353,7 +10447,11 @@
         <v>13.68</v>
       </c>
       <c r="H277" s="10" t="n"/>
-      <c r="I277" s="10" t="n"/>
+      <c r="I277" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="8" t="inlineStr">
@@ -9384,7 +10482,11 @@
         <v>10.08</v>
       </c>
       <c r="H278" s="10" t="n"/>
-      <c r="I278" s="10" t="n"/>
+      <c r="I278" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="8" t="inlineStr">
@@ -9415,7 +10517,11 @@
         <v>10.35</v>
       </c>
       <c r="H279" s="10" t="n"/>
-      <c r="I279" s="10" t="n"/>
+      <c r="I279" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="8" t="inlineStr">
@@ -9446,7 +10552,11 @@
         <v>13.91</v>
       </c>
       <c r="H280" s="10" t="n"/>
-      <c r="I280" s="10" t="n"/>
+      <c r="I280" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="8" t="inlineStr">
@@ -9477,7 +10587,11 @@
         <v>15.12</v>
       </c>
       <c r="H281" s="10" t="n"/>
-      <c r="I281" s="10" t="n"/>
+      <c r="I281" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="8" t="inlineStr">
@@ -9508,7 +10622,11 @@
         <v>18</v>
       </c>
       <c r="H282" s="10" t="n"/>
-      <c r="I282" s="10" t="n"/>
+      <c r="I282" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="8" t="inlineStr">
@@ -9539,7 +10657,11 @@
         <v>16.56</v>
       </c>
       <c r="H283" s="10" t="n"/>
-      <c r="I283" s="10" t="n"/>
+      <c r="I283" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="8" t="inlineStr">
@@ -9570,7 +10692,11 @@
         <v>12</v>
       </c>
       <c r="H284" s="10" t="n"/>
-      <c r="I284" s="10" t="n"/>
+      <c r="I284" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="8" t="inlineStr">
@@ -9601,7 +10727,11 @@
         <v>12.32</v>
       </c>
       <c r="H285" s="10" t="n"/>
-      <c r="I285" s="10" t="n"/>
+      <c r="I285" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="8" t="inlineStr">
@@ -9631,8 +10761,14 @@
       <c r="G286" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="H286" s="10" t="n"/>
-      <c r="I286" s="10" t="n"/>
+      <c r="H286" s="10" t="n">
+        <v>18.675</v>
+      </c>
+      <c r="I286" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 18.675 vs current 18.9</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="8" t="inlineStr">
@@ -9662,8 +10798,14 @@
       <c r="G287" s="9" t="n">
         <v>17.39</v>
       </c>
-      <c r="H287" s="10" t="n"/>
-      <c r="I287" s="10" t="n"/>
+      <c r="H287" s="10" t="n">
+        <v>17.181</v>
+      </c>
+      <c r="I287" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 17.181 vs current 17.39</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="8" t="inlineStr">
@@ -9694,7 +10836,11 @@
         <v>12.6</v>
       </c>
       <c r="H288" s="10" t="n"/>
-      <c r="I288" s="10" t="n"/>
+      <c r="I288" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="8" t="inlineStr">
@@ -9724,8 +10870,14 @@
       <c r="G289" s="9" t="n">
         <v>12.94</v>
       </c>
-      <c r="H289" s="10" t="n"/>
-      <c r="I289" s="10" t="n"/>
+      <c r="H289" s="10" t="n">
+        <v>12.782</v>
+      </c>
+      <c r="I289" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 12.782 vs current 12.94</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="8" t="inlineStr">
@@ -9756,7 +10908,11 @@
         <v>21.6</v>
       </c>
       <c r="H290" s="10" t="n"/>
-      <c r="I290" s="10" t="n"/>
+      <c r="I290" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="8" t="inlineStr">
@@ -9787,7 +10943,11 @@
         <v>19.87</v>
       </c>
       <c r="H291" s="10" t="n"/>
-      <c r="I291" s="10" t="n"/>
+      <c r="I291" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="8" t="inlineStr">
@@ -9818,7 +10978,11 @@
         <v>14.4</v>
       </c>
       <c r="H292" s="10" t="n"/>
-      <c r="I292" s="10" t="n"/>
+      <c r="I292" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="8" t="inlineStr">
@@ -9849,7 +11013,11 @@
         <v>18</v>
       </c>
       <c r="H293" s="10" t="n"/>
-      <c r="I293" s="10" t="n"/>
+      <c r="I293" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="8" t="inlineStr">
@@ -9880,7 +11048,11 @@
         <v>16.56</v>
       </c>
       <c r="H294" s="10" t="n"/>
-      <c r="I294" s="10" t="n"/>
+      <c r="I294" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="8" t="inlineStr">
@@ -9911,7 +11083,11 @@
         <v>12.32</v>
       </c>
       <c r="H295" s="10" t="n"/>
-      <c r="I295" s="10" t="n"/>
+      <c r="I295" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="8" t="inlineStr">
@@ -9942,7 +11118,11 @@
         <v>21.6</v>
       </c>
       <c r="H296" s="10" t="n"/>
-      <c r="I296" s="10" t="n"/>
+      <c r="I296" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="8" t="inlineStr">
@@ -9973,7 +11153,11 @@
         <v>19.87</v>
       </c>
       <c r="H297" s="10" t="n"/>
-      <c r="I297" s="10" t="n"/>
+      <c r="I297" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="8" t="inlineStr">
@@ -10004,7 +11188,11 @@
         <v>14.78</v>
       </c>
       <c r="H298" s="10" t="n"/>
-      <c r="I298" s="10" t="n"/>
+      <c r="I298" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="8" t="inlineStr">
@@ -10035,7 +11223,11 @@
         <v>25.2</v>
       </c>
       <c r="H299" s="10" t="n"/>
-      <c r="I299" s="10" t="n"/>
+      <c r="I299" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="8" t="inlineStr">
@@ -10066,7 +11258,11 @@
         <v>23.18</v>
       </c>
       <c r="H300" s="10" t="n"/>
-      <c r="I300" s="10" t="n"/>
+      <c r="I300" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="8" t="inlineStr">
@@ -10097,7 +11293,11 @@
         <v>17.25</v>
       </c>
       <c r="H301" s="10" t="n"/>
-      <c r="I301" s="10" t="n"/>
+      <c r="I301" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="8" t="inlineStr">
@@ -10128,7 +11328,11 @@
         <v>2.56</v>
       </c>
       <c r="H302" s="10" t="n"/>
-      <c r="I302" s="10" t="n"/>
+      <c r="I302" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="8" t="inlineStr">
@@ -10159,7 +11363,11 @@
         <v>3.53</v>
       </c>
       <c r="H303" s="10" t="n"/>
-      <c r="I303" s="10" t="n"/>
+      <c r="I303" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="8" t="inlineStr">
@@ -10190,7 +11398,11 @@
         <v>3.84</v>
       </c>
       <c r="H304" s="10" t="n"/>
-      <c r="I304" s="10" t="n"/>
+      <c r="I304" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="8" t="inlineStr">
@@ -10220,8 +11432,14 @@
       <c r="G305" s="9" t="n">
         <v>3.32</v>
       </c>
-      <c r="H305" s="10" t="n"/>
-      <c r="I305" s="10" t="n"/>
+      <c r="H305" s="10" t="n">
+        <v>3.192</v>
+      </c>
+      <c r="I305" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 3.192 vs current 3.32</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="8" t="inlineStr">
@@ -10251,8 +11469,14 @@
       <c r="G306" s="9" t="n">
         <v>4.98</v>
       </c>
-      <c r="H306" s="10" t="n"/>
-      <c r="I306" s="10" t="n"/>
+      <c r="H306" s="10" t="n">
+        <v>4.788</v>
+      </c>
+      <c r="I306" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.788 vs current 4.98</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="8" t="inlineStr">
@@ -10282,8 +11506,14 @@
       <c r="G307" s="9" t="n">
         <v>4.58</v>
       </c>
-      <c r="H307" s="10" t="n"/>
-      <c r="I307" s="10" t="n"/>
+      <c r="H307" s="10" t="n">
+        <v>4.405</v>
+      </c>
+      <c r="I307" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.405 vs current 4.58</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="8" t="inlineStr">
@@ -10313,8 +11543,14 @@
       <c r="G308" s="9" t="n">
         <v>3.79</v>
       </c>
-      <c r="H308" s="10" t="n"/>
-      <c r="I308" s="10" t="n"/>
+      <c r="H308" s="10" t="n">
+        <v>3.744</v>
+      </c>
+      <c r="I308" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 3.744 vs current 3.79</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="8" t="inlineStr">
@@ -10344,8 +11580,14 @@
       <c r="G309" s="9" t="n">
         <v>5.69</v>
       </c>
-      <c r="H309" s="10" t="n"/>
-      <c r="I309" s="10" t="n"/>
+      <c r="H309" s="10" t="n">
+        <v>5.616</v>
+      </c>
+      <c r="I309" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.616 vs current 5.69</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="8" t="inlineStr">
@@ -10375,8 +11617,14 @@
       <c r="G310" s="9" t="n">
         <v>5.23</v>
       </c>
-      <c r="H310" s="10" t="n"/>
-      <c r="I310" s="10" t="n"/>
+      <c r="H310" s="10" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="I310" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.167 vs current 5.23</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="8" t="inlineStr">
@@ -10406,8 +11654,14 @@
       <c r="G311" s="9" t="n">
         <v>4.27</v>
       </c>
-      <c r="H311" s="10" t="n"/>
-      <c r="I311" s="10" t="n"/>
+      <c r="H311" s="10" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="I311" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.212 vs current 4.27</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="8" t="inlineStr">
@@ -10437,8 +11691,14 @@
       <c r="G312" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="H312" s="10" t="n"/>
-      <c r="I312" s="10" t="n"/>
+      <c r="H312" s="10" t="n">
+        <v>6.318</v>
+      </c>
+      <c r="I312" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.318 vs current 6.4</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="8" t="inlineStr">
@@ -10468,8 +11728,14 @@
       <c r="G313" s="9" t="n">
         <v>5.89</v>
       </c>
-      <c r="H313" s="10" t="n"/>
-      <c r="I313" s="10" t="n"/>
+      <c r="H313" s="10" t="n">
+        <v>5.813</v>
+      </c>
+      <c r="I313" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.813 vs current 5.89</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="8" t="inlineStr">
@@ -10499,8 +11765,14 @@
       <c r="G314" s="9" t="n">
         <v>4.74</v>
       </c>
-      <c r="H314" s="10" t="n"/>
-      <c r="I314" s="10" t="n"/>
+      <c r="H314" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I314" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.68 vs current 4.74</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="8" t="inlineStr">
@@ -10531,7 +11803,11 @@
         <v>6.54</v>
       </c>
       <c r="H315" s="10" t="n"/>
-      <c r="I315" s="10" t="n"/>
+      <c r="I315" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
@@ -10562,7 +11838,11 @@
         <v>7.11</v>
       </c>
       <c r="H316" s="10" t="n"/>
-      <c r="I316" s="10" t="n"/>
+      <c r="I316" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="8" t="inlineStr">
@@ -10592,8 +11872,14 @@
       <c r="G317" s="9" t="n">
         <v>5.69</v>
       </c>
-      <c r="H317" s="10" t="n"/>
-      <c r="I317" s="10" t="n"/>
+      <c r="H317" s="10" t="n">
+        <v>5.616</v>
+      </c>
+      <c r="I317" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.616 vs current 5.69</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="8" t="inlineStr">
@@ -10623,8 +11909,14 @@
       <c r="G318" s="9" t="n">
         <v>7.85</v>
       </c>
-      <c r="H318" s="10" t="n"/>
-      <c r="I318" s="10" t="n"/>
+      <c r="H318" s="10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I318" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 7.75 vs current 7.85</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="8" t="inlineStr">
@@ -10654,8 +11946,14 @@
       <c r="G319" s="9" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="H319" s="10" t="n"/>
-      <c r="I319" s="10" t="n"/>
+      <c r="H319" s="10" t="n">
+        <v>8.423999999999999</v>
+      </c>
+      <c r="I319" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 8.424 vs current 8.53</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="8" t="inlineStr">
@@ -10686,7 +11984,11 @@
         <v>6.64</v>
       </c>
       <c r="H320" s="10" t="n"/>
-      <c r="I320" s="10" t="n"/>
+      <c r="I320" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="8" t="inlineStr">
@@ -10717,7 +12019,11 @@
         <v>9.16</v>
       </c>
       <c r="H321" s="10" t="n"/>
-      <c r="I321" s="10" t="n"/>
+      <c r="I321" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="8" t="inlineStr">
@@ -10748,7 +12054,11 @@
         <v>9.949999999999999</v>
       </c>
       <c r="H322" s="10" t="n"/>
-      <c r="I322" s="10" t="n"/>
+      <c r="I322" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="8" t="inlineStr">
@@ -10779,7 +12089,11 @@
         <v>2.92</v>
       </c>
       <c r="H323" s="10" t="n"/>
-      <c r="I323" s="10" t="n"/>
+      <c r="I323" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="8" t="inlineStr">
@@ -10810,7 +12124,11 @@
         <v>4.02</v>
       </c>
       <c r="H324" s="10" t="n"/>
-      <c r="I324" s="10" t="n"/>
+      <c r="I324" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="8" t="inlineStr">
@@ -10841,7 +12159,11 @@
         <v>4.37</v>
       </c>
       <c r="H325" s="10" t="n"/>
-      <c r="I325" s="10" t="n"/>
+      <c r="I325" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="8" t="inlineStr">
@@ -10872,7 +12194,11 @@
         <v>3.4</v>
       </c>
       <c r="H326" s="10" t="n"/>
-      <c r="I326" s="10" t="n"/>
+      <c r="I326" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="8" t="inlineStr">
@@ -10903,7 +12229,11 @@
         <v>4.69</v>
       </c>
       <c r="H327" s="10" t="n"/>
-      <c r="I327" s="10" t="n"/>
+      <c r="I327" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="8" t="inlineStr">
@@ -10934,7 +12264,11 @@
         <v>5.1</v>
       </c>
       <c r="H328" s="10" t="n"/>
-      <c r="I328" s="10" t="n"/>
+      <c r="I328" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="8" t="inlineStr">
@@ -10965,7 +12299,11 @@
         <v>3.89</v>
       </c>
       <c r="H329" s="10" t="n"/>
-      <c r="I329" s="10" t="n"/>
+      <c r="I329" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="8" t="inlineStr">
@@ -10996,7 +12334,11 @@
         <v>5.37</v>
       </c>
       <c r="H330" s="10" t="n"/>
-      <c r="I330" s="10" t="n"/>
+      <c r="I330" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="8" t="inlineStr">
@@ -11027,7 +12369,11 @@
         <v>5.83</v>
       </c>
       <c r="H331" s="10" t="n"/>
-      <c r="I331" s="10" t="n"/>
+      <c r="I331" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="8" t="inlineStr">
@@ -11058,7 +12404,11 @@
         <v>4.37</v>
       </c>
       <c r="H332" s="10" t="n"/>
-      <c r="I332" s="10" t="n"/>
+      <c r="I332" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="8" t="inlineStr">
@@ -11089,7 +12439,11 @@
         <v>6.04</v>
       </c>
       <c r="H333" s="10" t="n"/>
-      <c r="I333" s="10" t="n"/>
+      <c r="I333" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="8" t="inlineStr">
@@ -11120,7 +12474,11 @@
         <v>6.56</v>
       </c>
       <c r="H334" s="10" t="n"/>
-      <c r="I334" s="10" t="n"/>
+      <c r="I334" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="8" t="inlineStr">
@@ -11151,7 +12509,11 @@
         <v>5.83</v>
       </c>
       <c r="H335" s="10" t="n"/>
-      <c r="I335" s="10" t="n"/>
+      <c r="I335" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="8" t="inlineStr">
@@ -11182,7 +12544,11 @@
         <v>8.050000000000001</v>
       </c>
       <c r="H336" s="10" t="n"/>
-      <c r="I336" s="10" t="n"/>
+      <c r="I336" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="8" t="inlineStr">
@@ -11213,7 +12579,11 @@
         <v>8.75</v>
       </c>
       <c r="H337" s="10" t="n"/>
-      <c r="I337" s="10" t="n"/>
+      <c r="I337" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: RNG PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="8" t="inlineStr">
@@ -11243,8 +12613,14 @@
       <c r="G338" s="9" t="n">
         <v>3.98</v>
       </c>
-      <c r="H338" s="10" t="n"/>
-      <c r="I338" s="10" t="n"/>
+      <c r="H338" s="10" t="n">
+        <v>4.032</v>
+      </c>
+      <c r="I338" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.032 vs current 3.98</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="8" t="inlineStr">
@@ -11274,8 +12650,14 @@
       <c r="G339" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="H339" s="10" t="n"/>
-      <c r="I339" s="10" t="n"/>
+      <c r="H339" s="10" t="n">
+        <v>5.564</v>
+      </c>
+      <c r="I339" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.564 vs current 5.5</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="8" t="inlineStr">
@@ -11305,8 +12687,14 @@
       <c r="G340" s="9" t="n">
         <v>5.98</v>
       </c>
-      <c r="H340" s="10" t="n"/>
-      <c r="I340" s="10" t="n"/>
+      <c r="H340" s="10" t="n">
+        <v>6.048</v>
+      </c>
+      <c r="I340" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.048 vs current 5.98</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="8" t="inlineStr">
@@ -11336,8 +12724,14 @@
       <c r="G341" s="9" t="n">
         <v>4.37</v>
       </c>
-      <c r="H341" s="10" t="n"/>
-      <c r="I341" s="10" t="n"/>
+      <c r="H341" s="10" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="I341" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.428 vs current 4.37</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="8" t="inlineStr">
@@ -11367,8 +12761,14 @@
       <c r="G342" s="9" t="n">
         <v>6.04</v>
       </c>
-      <c r="H342" s="10" t="n"/>
-      <c r="I342" s="10" t="n"/>
+      <c r="H342" s="10" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="I342" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.111 vs current 6.04</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="8" t="inlineStr">
@@ -11398,8 +12798,14 @@
       <c r="G343" s="9" t="n">
         <v>6.56</v>
       </c>
-      <c r="H343" s="10" t="n"/>
-      <c r="I343" s="10" t="n"/>
+      <c r="H343" s="10" t="n">
+        <v>6.642</v>
+      </c>
+      <c r="I343" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.642 vs current 6.56</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="8" t="inlineStr">
@@ -11429,8 +12835,14 @@
       <c r="G344" s="9" t="n">
         <v>4.68</v>
       </c>
-      <c r="H344" s="10" t="n"/>
-      <c r="I344" s="10" t="n"/>
+      <c r="H344" s="10" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I344" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.92 vs current 4.68</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="8" t="inlineStr">
@@ -11460,8 +12872,14 @@
       <c r="G345" s="9" t="n">
         <v>6.46</v>
       </c>
-      <c r="H345" s="10" t="n"/>
-      <c r="I345" s="10" t="n"/>
+      <c r="H345" s="10" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="I345" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.79 vs current 6.46</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="8" t="inlineStr">
@@ -11491,8 +12909,14 @@
       <c r="G346" s="9" t="n">
         <v>5.49</v>
       </c>
-      <c r="H346" s="10" t="n"/>
-      <c r="I346" s="10" t="n"/>
+      <c r="H346" s="10" t="n">
+        <v>5.773</v>
+      </c>
+      <c r="I346" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.773 vs current 5.49</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="8" t="inlineStr">
@@ -11522,8 +12946,14 @@
       <c r="G347" s="9" t="n">
         <v>8.42</v>
       </c>
-      <c r="H347" s="10" t="n"/>
-      <c r="I347" s="10" t="n"/>
+      <c r="H347" s="10" t="n">
+        <v>8.856</v>
+      </c>
+      <c r="I347" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 8.856 vs current 8.42</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
@@ -11553,8 +12983,14 @@
       <c r="G348" s="9" t="n">
         <v>7.75</v>
       </c>
-      <c r="H348" s="10" t="n"/>
-      <c r="I348" s="10" t="n"/>
+      <c r="H348" s="10" t="n">
+        <v>8.148</v>
+      </c>
+      <c r="I348" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 8.148 vs current 7.75</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="8" t="inlineStr">
@@ -11584,8 +13020,14 @@
       <c r="G349" s="9" t="n">
         <v>5.62</v>
       </c>
-      <c r="H349" s="10" t="n"/>
-      <c r="I349" s="10" t="n"/>
+      <c r="H349" s="10" t="n">
+        <v>5.904</v>
+      </c>
+      <c r="I349" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.904 vs current 5.62</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="8" t="inlineStr">
@@ -11615,8 +13057,14 @@
       <c r="G350" s="9" t="n">
         <v>6.08</v>
       </c>
-      <c r="H350" s="10" t="n"/>
-      <c r="I350" s="10" t="n"/>
+      <c r="H350" s="10" t="n">
+        <v>6.396</v>
+      </c>
+      <c r="I350" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.396 vs current 6.08</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="8" t="inlineStr">
@@ -11646,8 +13094,14 @@
       <c r="G351" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="H351" s="10" t="n"/>
-      <c r="I351" s="10" t="n"/>
+      <c r="H351" s="10" t="n">
+        <v>8.826000000000001</v>
+      </c>
+      <c r="I351" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 8.826 vs current 8.4</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="8" t="inlineStr">
@@ -11677,8 +13131,14 @@
       <c r="G352" s="9" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="H352" s="10" t="n"/>
-      <c r="I352" s="10" t="n"/>
+      <c r="H352" s="10" t="n">
+        <v>9.593999999999999</v>
+      </c>
+      <c r="I352" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 9.594 vs current 9.13</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="8" t="inlineStr">
@@ -11708,8 +13168,14 @@
       <c r="G353" s="9" t="n">
         <v>7.14</v>
       </c>
-      <c r="H353" s="10" t="n"/>
-      <c r="I353" s="10" t="n"/>
+      <c r="H353" s="10" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="I353" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 7.505 vs current 7.14</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="8" t="inlineStr">
@@ -11739,8 +13205,14 @@
       <c r="G354" s="9" t="n">
         <v>7.35</v>
       </c>
-      <c r="H354" s="10" t="n"/>
-      <c r="I354" s="10" t="n"/>
+      <c r="H354" s="10" t="n">
+        <v>7.724</v>
+      </c>
+      <c r="I354" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 7.724 vs current 7.35</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="8" t="inlineStr">
@@ -11770,8 +13242,14 @@
       <c r="G355" s="9" t="n">
         <v>10.14</v>
       </c>
-      <c r="H355" s="10" t="n"/>
-      <c r="I355" s="10" t="n"/>
+      <c r="H355" s="10" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="I355" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 10.66 vs current 10.14</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="8" t="inlineStr">
@@ -11801,8 +13279,14 @@
       <c r="G356" s="9" t="n">
         <v>11.02</v>
       </c>
-      <c r="H356" s="10" t="n"/>
-      <c r="I356" s="10" t="n"/>
+      <c r="H356" s="10" t="n">
+        <v>11.587</v>
+      </c>
+      <c r="I356" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 11.587 vs current 11.02</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="8" t="inlineStr">
@@ -11832,8 +13316,14 @@
       <c r="G357" s="9" t="n">
         <v>11.93</v>
       </c>
-      <c r="H357" s="10" t="n"/>
-      <c r="I357" s="10" t="n"/>
+      <c r="H357" s="10" t="n">
+        <v>12.087</v>
+      </c>
+      <c r="I357" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 12.087 vs current 11.93</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="8" t="inlineStr">
@@ -11863,8 +13353,14 @@
       <c r="G358" s="9" t="n">
         <v>10.98</v>
       </c>
-      <c r="H358" s="10" t="n"/>
-      <c r="I358" s="10" t="n"/>
+      <c r="H358" s="10" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="I358" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 11.12 vs current 10.98</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="8" t="inlineStr">
@@ -11894,8 +13390,14 @@
       <c r="G359" s="9" t="n">
         <v>7.96</v>
       </c>
-      <c r="H359" s="10" t="n"/>
-      <c r="I359" s="10" t="n"/>
+      <c r="H359" s="10" t="n">
+        <v>8.058</v>
+      </c>
+      <c r="I359" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 8.058 vs current 7.96</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="8" t="inlineStr">
@@ -11925,8 +13427,14 @@
       <c r="G360" s="9" t="n">
         <v>9.24</v>
       </c>
-      <c r="H360" s="10" t="n"/>
-      <c r="I360" s="10" t="n"/>
+      <c r="H360" s="10" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="I360" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 9.48 vs current 9.24</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="8" t="inlineStr">
@@ -11956,8 +13464,14 @@
       <c r="G361" s="9" t="n">
         <v>12.75</v>
       </c>
-      <c r="H361" s="10" t="n"/>
-      <c r="I361" s="10" t="n"/>
+      <c r="H361" s="10" t="n">
+        <v>13.082</v>
+      </c>
+      <c r="I361" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 13.082 vs current 12.75</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="8" t="inlineStr">
@@ -11987,8 +13501,14 @@
       <c r="G362" s="9" t="n">
         <v>13.86</v>
       </c>
-      <c r="H362" s="10" t="n"/>
-      <c r="I362" s="10" t="n"/>
+      <c r="H362" s="10" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="I362" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 14.22 vs current 13.86</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="8" t="inlineStr">
@@ -12018,8 +13538,14 @@
       <c r="G363" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H363" s="10" t="n"/>
-      <c r="I363" s="10" t="n"/>
+      <c r="H363" s="10" t="n">
+        <v>9.954000000000001</v>
+      </c>
+      <c r="I363" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 9.954 vs current 9.7</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="8" t="inlineStr">
@@ -12049,8 +13575,14 @@
       <c r="G364" s="9" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="H364" s="10" t="n"/>
-      <c r="I364" s="10" t="n"/>
+      <c r="H364" s="10" t="n">
+        <v>10.219</v>
+      </c>
+      <c r="I364" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 10.219 vs current 9.96</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="8" t="inlineStr">
@@ -12080,8 +13612,14 @@
       <c r="G365" s="9" t="n">
         <v>13.39</v>
       </c>
-      <c r="H365" s="10" t="n"/>
-      <c r="I365" s="10" t="n"/>
+      <c r="H365" s="10" t="n">
+        <v>13.737</v>
+      </c>
+      <c r="I365" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 13.737 vs current 13.39</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="8" t="inlineStr">
@@ -12111,8 +13649,14 @@
       <c r="G366" s="9" t="n">
         <v>14.55</v>
       </c>
-      <c r="H366" s="10" t="n"/>
-      <c r="I366" s="10" t="n"/>
+      <c r="H366" s="10" t="n">
+        <v>14.931</v>
+      </c>
+      <c r="I366" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 14.931 vs current 14.55</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="8" t="inlineStr">
@@ -12142,8 +13686,14 @@
       <c r="G367" s="9" t="n">
         <v>17.32</v>
       </c>
-      <c r="H367" s="10" t="n"/>
-      <c r="I367" s="10" t="n"/>
+      <c r="H367" s="10" t="n">
+        <v>17.775</v>
+      </c>
+      <c r="I367" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 17.775 vs current 17.32</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="8" t="inlineStr">
@@ -12173,8 +13723,14 @@
       <c r="G368" s="9" t="n">
         <v>15.94</v>
       </c>
-      <c r="H368" s="10" t="n"/>
-      <c r="I368" s="10" t="n"/>
+      <c r="H368" s="10" t="n">
+        <v>16.353</v>
+      </c>
+      <c r="I368" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 16.353 vs current 15.94</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="8" t="inlineStr">
@@ -12204,8 +13760,14 @@
       <c r="G369" s="9" t="n">
         <v>11.55</v>
       </c>
-      <c r="H369" s="10" t="n"/>
-      <c r="I369" s="10" t="n"/>
+      <c r="H369" s="10" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="I369" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 11.85 vs current 11.55</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="8" t="inlineStr">
@@ -12235,8 +13797,14 @@
       <c r="G370" s="9" t="n">
         <v>11.86</v>
       </c>
-      <c r="H370" s="10" t="n"/>
-      <c r="I370" s="10" t="n"/>
+      <c r="H370" s="10" t="n">
+        <v>12.166</v>
+      </c>
+      <c r="I370" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 12.166 vs current 11.86</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="8" t="inlineStr">
@@ -12266,8 +13834,14 @@
       <c r="G371" s="9" t="n">
         <v>20.79</v>
       </c>
-      <c r="H371" s="10" t="n"/>
-      <c r="I371" s="10" t="n"/>
+      <c r="H371" s="10" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="I371" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 21.33 vs current 20.79</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="8" t="inlineStr">
@@ -12297,8 +13871,14 @@
       <c r="G372" s="9" t="n">
         <v>19.13</v>
       </c>
-      <c r="H372" s="10" t="n"/>
-      <c r="I372" s="10" t="n"/>
+      <c r="H372" s="10" t="n">
+        <v>19.624</v>
+      </c>
+      <c r="I372" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 19.624 vs current 19.13</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="8" t="inlineStr">
@@ -12328,8 +13908,14 @@
       <c r="G373" s="9" t="n">
         <v>13.86</v>
       </c>
-      <c r="H373" s="10" t="n"/>
-      <c r="I373" s="10" t="n"/>
+      <c r="H373" s="10" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="I373" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 14.22 vs current 13.86</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="8" t="inlineStr">
@@ -12359,8 +13945,14 @@
       <c r="G374" s="9" t="n">
         <v>17.32</v>
       </c>
-      <c r="H374" s="10" t="n"/>
-      <c r="I374" s="10" t="n"/>
+      <c r="H374" s="10" t="n">
+        <v>17.775</v>
+      </c>
+      <c r="I374" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 17.775 vs current 17.32</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="8" t="inlineStr">
@@ -12390,8 +13982,14 @@
       <c r="G375" s="9" t="n">
         <v>15.94</v>
       </c>
-      <c r="H375" s="10" t="n"/>
-      <c r="I375" s="10" t="n"/>
+      <c r="H375" s="10" t="n">
+        <v>16.353</v>
+      </c>
+      <c r="I375" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 16.353 vs current 15.94</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="8" t="inlineStr">
@@ -12421,8 +14019,14 @@
       <c r="G376" s="9" t="n">
         <v>11.86</v>
       </c>
-      <c r="H376" s="10" t="n"/>
-      <c r="I376" s="10" t="n"/>
+      <c r="H376" s="10" t="n">
+        <v>12.166</v>
+      </c>
+      <c r="I376" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 12.166 vs current 11.86</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="8" t="inlineStr">
@@ -12452,8 +14056,14 @@
       <c r="G377" s="9" t="n">
         <v>20.79</v>
       </c>
-      <c r="H377" s="10" t="n"/>
-      <c r="I377" s="10" t="n"/>
+      <c r="H377" s="10" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="I377" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 21.33 vs current 20.79</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="8" t="inlineStr">
@@ -12483,8 +14093,14 @@
       <c r="G378" s="9" t="n">
         <v>19.13</v>
       </c>
-      <c r="H378" s="10" t="n"/>
-      <c r="I378" s="10" t="n"/>
+      <c r="H378" s="10" t="n">
+        <v>19.624</v>
+      </c>
+      <c r="I378" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 19.624 vs current 19.13</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="8" t="inlineStr">
@@ -12515,7 +14131,11 @@
         <v>14.23</v>
       </c>
       <c r="H379" s="10" t="n"/>
-      <c r="I379" s="10" t="n"/>
+      <c r="I379" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="8" t="inlineStr">
@@ -12546,7 +14166,11 @@
         <v>24.25</v>
       </c>
       <c r="H380" s="10" t="n"/>
-      <c r="I380" s="10" t="n"/>
+      <c r="I380" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="8" t="inlineStr">
@@ -12577,7 +14201,11 @@
         <v>22.31</v>
       </c>
       <c r="H381" s="10" t="n"/>
-      <c r="I381" s="10" t="n"/>
+      <c r="I381" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="8" t="inlineStr">
@@ -12608,7 +14236,11 @@
         <v>16.6</v>
       </c>
       <c r="H382" s="10" t="n"/>
-      <c r="I382" s="10" t="n"/>
+      <c r="I382" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="8" t="inlineStr">
@@ -12639,7 +14271,11 @@
         <v>14.23</v>
       </c>
       <c r="H383" s="10" t="n"/>
-      <c r="I383" s="10" t="n"/>
+      <c r="I383" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="8" t="inlineStr">
@@ -12669,8 +14305,14 @@
       <c r="G384" s="9" t="n">
         <v>19.13</v>
       </c>
-      <c r="H384" s="10" t="n"/>
-      <c r="I384" s="10" t="n"/>
+      <c r="H384" s="10" t="n">
+        <v>19.624</v>
+      </c>
+      <c r="I384" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 19.624 vs current 19.13</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="8" t="inlineStr">
@@ -12700,8 +14342,14 @@
       <c r="G385" s="9" t="n">
         <v>20.79</v>
       </c>
-      <c r="H385" s="10" t="n"/>
-      <c r="I385" s="10" t="n"/>
+      <c r="H385" s="10" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="I385" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 21.33 vs current 20.79</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="8" t="inlineStr">
@@ -12732,7 +14380,11 @@
         <v>30.2</v>
       </c>
       <c r="H386" s="10" t="n"/>
-      <c r="I386" s="10" t="n"/>
+      <c r="I386" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="8" t="inlineStr">
@@ -12762,8 +14414,14 @@
       <c r="G387" s="9" t="n">
         <v>11.86</v>
       </c>
-      <c r="H387" s="10" t="n"/>
-      <c r="I387" s="10" t="n"/>
+      <c r="H387" s="10" t="n">
+        <v>12.166</v>
+      </c>
+      <c r="I387" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 12.166 vs current 11.86</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="8" t="inlineStr">
@@ -12793,8 +14451,14 @@
       <c r="G388" s="9" t="n">
         <v>15.94</v>
       </c>
-      <c r="H388" s="10" t="n"/>
-      <c r="I388" s="10" t="n"/>
+      <c r="H388" s="10" t="n">
+        <v>16.353</v>
+      </c>
+      <c r="I388" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 16.353 vs current 15.94</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="8" t="inlineStr">
@@ -12824,8 +14488,14 @@
       <c r="G389" s="9" t="n">
         <v>17.32</v>
       </c>
-      <c r="H389" s="10" t="n"/>
-      <c r="I389" s="10" t="n"/>
+      <c r="H389" s="10" t="n">
+        <v>17.775</v>
+      </c>
+      <c r="I389" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 17.775 vs current 17.32</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="8" t="inlineStr">
@@ -12856,7 +14526,11 @@
         <v>25.16</v>
       </c>
       <c r="H390" s="10" t="n"/>
-      <c r="I390" s="10" t="n"/>
+      <c r="I390" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="8" t="inlineStr">
@@ -12887,7 +14561,11 @@
         <v>11.86</v>
       </c>
       <c r="H391" s="10" t="n"/>
-      <c r="I391" s="10" t="n"/>
+      <c r="I391" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="8" t="inlineStr">
@@ -12918,7 +14596,11 @@
         <v>15.94</v>
       </c>
       <c r="H392" s="10" t="n"/>
-      <c r="I392" s="10" t="n"/>
+      <c r="I392" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="8" t="inlineStr">
@@ -12949,7 +14631,11 @@
         <v>18.29</v>
       </c>
       <c r="H393" s="10" t="n"/>
-      <c r="I393" s="10" t="n"/>
+      <c r="I393" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="8" t="inlineStr">
@@ -12980,7 +14666,11 @@
         <v>25.16</v>
       </c>
       <c r="H394" s="10" t="n"/>
-      <c r="I394" s="10" t="n"/>
+      <c r="I394" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="8" t="inlineStr">
@@ -13010,8 +14700,14 @@
       <c r="G395" s="9" t="n">
         <v>14.14</v>
       </c>
-      <c r="H395" s="10" t="n"/>
-      <c r="I395" s="10" t="n"/>
+      <c r="H395" s="10" t="n">
+        <v>13.281</v>
+      </c>
+      <c r="I395" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 13.281 vs current 14.14</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="8" t="inlineStr">
@@ -13041,8 +14737,14 @@
       <c r="G396" s="9" t="n">
         <v>19.01</v>
       </c>
-      <c r="H396" s="10" t="n"/>
-      <c r="I396" s="10" t="n"/>
+      <c r="H396" s="10" t="n">
+        <v>17.852</v>
+      </c>
+      <c r="I396" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 17.852 vs current 19.01</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="8" t="inlineStr">
@@ -13072,8 +14774,14 @@
       <c r="G397" s="9" t="n">
         <v>21.81</v>
       </c>
-      <c r="H397" s="10" t="n"/>
-      <c r="I397" s="10" t="n"/>
+      <c r="H397" s="10" t="n">
+        <v>20.482</v>
+      </c>
+      <c r="I397" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 20.482 vs current 21.81</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="8" t="inlineStr">
@@ -13103,8 +14811,14 @@
       <c r="G398" s="9" t="n">
         <v>30.01</v>
       </c>
-      <c r="H398" s="10" t="n"/>
-      <c r="I398" s="10" t="n"/>
+      <c r="H398" s="10" t="n">
+        <v>28.184</v>
+      </c>
+      <c r="I398" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 28.184 vs current 30.01</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="8" t="inlineStr">
@@ -13134,8 +14848,14 @@
       <c r="G399" s="9" t="n">
         <v>15.15</v>
       </c>
-      <c r="H399" s="10" t="n"/>
-      <c r="I399" s="10" t="n"/>
+      <c r="H399" s="10" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="I399" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 14.23 vs current 15.15</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="8" t="inlineStr">
@@ -13165,8 +14885,14 @@
       <c r="G400" s="9" t="n">
         <v>20.37</v>
       </c>
-      <c r="H400" s="10" t="n"/>
-      <c r="I400" s="10" t="n"/>
+      <c r="H400" s="10" t="n">
+        <v>19.127</v>
+      </c>
+      <c r="I400" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 19.127 vs current 20.37</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="8" t="inlineStr">
@@ -13196,8 +14922,14 @@
       <c r="G401" s="9" t="n">
         <v>23.37</v>
       </c>
-      <c r="H401" s="10" t="n"/>
-      <c r="I401" s="10" t="n"/>
+      <c r="H401" s="10" t="n">
+        <v>21.945</v>
+      </c>
+      <c r="I401" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 21.945 vs current 23.37</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="8" t="inlineStr">
@@ -13227,8 +14959,14 @@
       <c r="G402" s="9" t="n">
         <v>32.16</v>
       </c>
-      <c r="H402" s="10" t="n"/>
-      <c r="I402" s="10" t="n"/>
+      <c r="H402" s="10" t="n">
+        <v>30.197</v>
+      </c>
+      <c r="I402" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 30.197 vs current 32.16</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="8" t="inlineStr">
@@ -13259,7 +14997,11 @@
         <v>3.19</v>
       </c>
       <c r="H403" s="10" t="n"/>
-      <c r="I403" s="10" t="n"/>
+      <c r="I403" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="8" t="inlineStr">
@@ -13290,7 +15032,11 @@
         <v>4.79</v>
       </c>
       <c r="H404" s="10" t="n"/>
-      <c r="I404" s="10" t="n"/>
+      <c r="I404" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="8" t="inlineStr">
@@ -13321,7 +15067,11 @@
         <v>4.4</v>
       </c>
       <c r="H405" s="10" t="n"/>
-      <c r="I405" s="10" t="n"/>
+      <c r="I405" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="8" t="inlineStr">
@@ -13351,8 +15101,14 @@
       <c r="G406" s="9" t="n">
         <v>3.65</v>
       </c>
-      <c r="H406" s="10" t="n"/>
-      <c r="I406" s="10" t="n"/>
+      <c r="H406" s="10" t="n">
+        <v>3.744</v>
+      </c>
+      <c r="I406" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 3.744 vs current 3.65</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="8" t="inlineStr">
@@ -13382,8 +15138,14 @@
       <c r="G407" s="9" t="n">
         <v>5.47</v>
       </c>
-      <c r="H407" s="10" t="n"/>
-      <c r="I407" s="10" t="n"/>
+      <c r="H407" s="10" t="n">
+        <v>5.616</v>
+      </c>
+      <c r="I407" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.616 vs current 5.47</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="8" t="inlineStr">
@@ -13413,8 +15175,14 @@
       <c r="G408" s="9" t="n">
         <v>5.03</v>
       </c>
-      <c r="H408" s="10" t="n"/>
-      <c r="I408" s="10" t="n"/>
+      <c r="H408" s="10" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="I408" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.167 vs current 5.03</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="8" t="inlineStr">
@@ -13444,8 +15212,14 @@
       <c r="G409" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="H409" s="10" t="n"/>
-      <c r="I409" s="10" t="n"/>
+      <c r="H409" s="10" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="I409" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.212 vs current 4.1</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="8" t="inlineStr">
@@ -13475,8 +15249,14 @@
       <c r="G410" s="9" t="n">
         <v>6.16</v>
       </c>
-      <c r="H410" s="10" t="n"/>
-      <c r="I410" s="10" t="n"/>
+      <c r="H410" s="10" t="n">
+        <v>6.318</v>
+      </c>
+      <c r="I410" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 6.318 vs current 6.16</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="8" t="inlineStr">
@@ -13506,8 +15286,14 @@
       <c r="G411" s="9" t="n">
         <v>5.66</v>
       </c>
-      <c r="H411" s="10" t="n"/>
-      <c r="I411" s="10" t="n"/>
+      <c r="H411" s="10" t="n">
+        <v>5.813</v>
+      </c>
+      <c r="I411" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.813 vs current 5.66</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="8" t="inlineStr">
@@ -13537,8 +15323,14 @@
       <c r="G412" s="9" t="n">
         <v>4.56</v>
       </c>
-      <c r="H412" s="10" t="n"/>
-      <c r="I412" s="10" t="n"/>
+      <c r="H412" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I412" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 4.68 vs current 4.56</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="8" t="inlineStr">
@@ -13568,8 +15360,14 @@
       <c r="G413" s="9" t="n">
         <v>5.47</v>
       </c>
-      <c r="H413" s="10" t="n"/>
-      <c r="I413" s="10" t="n"/>
+      <c r="H413" s="10" t="n">
+        <v>5.616</v>
+      </c>
+      <c r="I413" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 5.616 vs current 5.47</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="8" t="inlineStr">
@@ -13599,8 +15397,14 @@
       <c r="G414" s="9" t="n">
         <v>7.55</v>
       </c>
-      <c r="H414" s="10" t="n"/>
-      <c r="I414" s="10" t="n"/>
+      <c r="H414" s="10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I414" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 7.75 vs current 7.55</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="8" t="inlineStr">
@@ -13630,8 +15434,14 @@
       <c r="G415" s="9" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="H415" s="10" t="n"/>
-      <c r="I415" s="10" t="n"/>
+      <c r="H415" s="10" t="n">
+        <v>8.423999999999999</v>
+      </c>
+      <c r="I415" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: Krishna Vanijya Pvt. Ltd. · lead 1 Day · source Rs 8.424 vs current 8.21</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="8" t="inlineStr">
@@ -13662,7 +15472,11 @@
         <v>2.74</v>
       </c>
       <c r="H416" s="10" t="n"/>
-      <c r="I416" s="10" t="n"/>
+      <c r="I416" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="8" t="inlineStr">
@@ -13693,7 +15507,11 @@
         <v>3.78</v>
       </c>
       <c r="H417" s="10" t="n"/>
-      <c r="I417" s="10" t="n"/>
+      <c r="I417" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="8" t="inlineStr">
@@ -13724,7 +15542,11 @@
         <v>4.1</v>
       </c>
       <c r="H418" s="10" t="n"/>
-      <c r="I418" s="10" t="n"/>
+      <c r="I418" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="8" t="inlineStr">
@@ -13755,7 +15577,11 @@
         <v>3.19</v>
       </c>
       <c r="H419" s="10" t="n"/>
-      <c r="I419" s="10" t="n"/>
+      <c r="I419" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="8" t="inlineStr">
@@ -13786,7 +15612,11 @@
         <v>4.4</v>
       </c>
       <c r="H420" s="10" t="n"/>
-      <c r="I420" s="10" t="n"/>
+      <c r="I420" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="8" t="inlineStr">
@@ -13817,7 +15647,11 @@
         <v>4.79</v>
       </c>
       <c r="H421" s="10" t="n"/>
-      <c r="I421" s="10" t="n"/>
+      <c r="I421" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="8" t="inlineStr">
@@ -13848,7 +15682,11 @@
         <v>3.65</v>
       </c>
       <c r="H422" s="10" t="n"/>
-      <c r="I422" s="10" t="n"/>
+      <c r="I422" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="8" t="inlineStr">
@@ -13879,7 +15717,11 @@
         <v>5.03</v>
       </c>
       <c r="H423" s="10" t="n"/>
-      <c r="I423" s="10" t="n"/>
+      <c r="I423" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="8" t="inlineStr">
@@ -13910,7 +15752,11 @@
         <v>5.47</v>
       </c>
       <c r="H424" s="10" t="n"/>
-      <c r="I424" s="10" t="n"/>
+      <c r="I424" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="8" t="inlineStr">
@@ -13941,7 +15787,11 @@
         <v>4.1</v>
       </c>
       <c r="H425" s="10" t="n"/>
-      <c r="I425" s="10" t="n"/>
+      <c r="I425" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="8" t="inlineStr">
@@ -13972,7 +15822,11 @@
         <v>5.66</v>
       </c>
       <c r="H426" s="10" t="n"/>
-      <c r="I426" s="10" t="n"/>
+      <c r="I426" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="8" t="inlineStr">
@@ -14003,7 +15857,11 @@
         <v>6.16</v>
       </c>
       <c r="H427" s="10" t="n"/>
-      <c r="I427" s="10" t="n"/>
+      <c r="I427" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="8" t="inlineStr">
@@ -14034,7 +15892,11 @@
         <v>5.47</v>
       </c>
       <c r="H428" s="10" t="n"/>
-      <c r="I428" s="10" t="n"/>
+      <c r="I428" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="8" t="inlineStr">
@@ -14065,7 +15927,11 @@
         <v>7.55</v>
       </c>
       <c r="H429" s="10" t="n"/>
-      <c r="I429" s="10" t="n"/>
+      <c r="I429" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="8" t="inlineStr">
@@ -14096,7 +15962,11 @@
         <v>7.55</v>
       </c>
       <c r="H430" s="10" t="n"/>
-      <c r="I430" s="10" t="n"/>
+      <c r="I430" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="8" t="inlineStr">
@@ -14127,7 +15997,11 @@
         <v>7.13</v>
       </c>
       <c r="H431" s="10" t="n"/>
-      <c r="I431" s="10" t="n"/>
+      <c r="I431" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="8" t="inlineStr">
@@ -14158,7 +16032,11 @@
         <v>6.56</v>
       </c>
       <c r="H432" s="10" t="n"/>
-      <c r="I432" s="10" t="n"/>
+      <c r="I432" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="8" t="inlineStr">
@@ -14189,7 +16067,11 @@
         <v>9.82</v>
       </c>
       <c r="H433" s="10" t="n"/>
-      <c r="I433" s="10" t="n"/>
+      <c r="I433" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PARAMOUNT PAPER · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="8" t="inlineStr">
@@ -14216,7 +16098,11 @@
         <v>8.58</v>
       </c>
       <c r="H434" s="10" t="n"/>
-      <c r="I434" s="10" t="n"/>
+      <c r="I434" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: F.AHMED PAPER HOUSE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="8" t="inlineStr">
@@ -14247,7 +16133,11 @@
         <v>20.46</v>
       </c>
       <c r="H435" s="10" t="n"/>
-      <c r="I435" s="10" t="n"/>
+      <c r="I435" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: F.AHMED PAPER HOUSE · lead 2 Day</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="8" t="inlineStr">
@@ -14278,7 +16168,11 @@
         <v>16.44</v>
       </c>
       <c r="H436" s="10" t="n"/>
-      <c r="I436" s="10" t="n"/>
+      <c r="I436" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: F.AHMED PAPER HOUSE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="8" t="inlineStr">
@@ -14309,7 +16203,11 @@
         <v>15.13</v>
       </c>
       <c r="H437" s="10" t="n"/>
-      <c r="I437" s="10" t="n"/>
+      <c r="I437" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: F.AHMED PAPER HOUSE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="8" t="inlineStr">
@@ -14340,7 +16238,11 @@
         <v>11.25</v>
       </c>
       <c r="H438" s="10" t="n"/>
-      <c r="I438" s="10" t="n"/>
+      <c r="I438" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: F.AHMED PAPER HOUSE · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="8" t="inlineStr">
@@ -14371,7 +16273,11 @@
         <v>11.45</v>
       </c>
       <c r="H439" s="10" t="n"/>
-      <c r="I439" s="10" t="n"/>
+      <c r="I439" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="8" t="inlineStr">
@@ -14402,7 +16308,11 @@
         <v>4.39</v>
       </c>
       <c r="H440" s="10" t="n"/>
-      <c r="I440" s="10" t="n"/>
+      <c r="I440" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="8" t="inlineStr">
@@ -14433,7 +16343,11 @@
         <v>3.46</v>
       </c>
       <c r="H441" s="10" t="n"/>
-      <c r="I441" s="10" t="n"/>
+      <c r="I441" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="8" t="inlineStr">
@@ -14464,7 +16378,11 @@
         <v>3.51</v>
       </c>
       <c r="H442" s="10" t="n"/>
-      <c r="I442" s="10" t="n"/>
+      <c r="I442" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="8" t="inlineStr">
@@ -14495,7 +16413,11 @@
         <v>16.22</v>
       </c>
       <c r="H443" s="10" t="n"/>
-      <c r="I443" s="10" t="n"/>
+      <c r="I443" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="8" t="inlineStr">
@@ -14526,7 +16448,11 @@
         <v>16.22</v>
       </c>
       <c r="H444" s="10" t="n"/>
-      <c r="I444" s="10" t="n"/>
+      <c r="I444" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="8" t="inlineStr">
@@ -14557,7 +16483,11 @@
         <v>0</v>
       </c>
       <c r="H445" s="10" t="n"/>
-      <c r="I445" s="10" t="n"/>
+      <c r="I445" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: PANNALAL SEAL &amp; SONS · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="8" t="inlineStr">
@@ -14588,7 +16518,11 @@
         <v>21.33</v>
       </c>
       <c r="H446" s="10" t="n"/>
-      <c r="I446" s="10" t="n"/>
+      <c r="I446" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="8" t="inlineStr">
@@ -14619,7 +16553,11 @@
         <v>19.62</v>
       </c>
       <c r="H447" s="10" t="n"/>
-      <c r="I447" s="10" t="n"/>
+      <c r="I447" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="8" t="inlineStr">
@@ -14650,7 +16588,11 @@
         <v>24.89</v>
       </c>
       <c r="H448" s="10" t="n"/>
-      <c r="I448" s="10" t="n"/>
+      <c r="I448" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="8" t="inlineStr">
@@ -14681,7 +16623,11 @@
         <v>22.89</v>
       </c>
       <c r="H449" s="10" t="n"/>
-      <c r="I449" s="10" t="n"/>
+      <c r="I449" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="8" t="inlineStr">
@@ -14712,7 +16658,11 @@
         <v>22.75</v>
       </c>
       <c r="H450" s="10" t="n"/>
-      <c r="I450" s="10" t="n"/>
+      <c r="I450" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="8" t="inlineStr">
@@ -14743,7 +16693,11 @@
         <v>8.85</v>
       </c>
       <c r="H451" s="10" t="n"/>
-      <c r="I451" s="10" t="n"/>
+      <c r="I451" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="8" t="inlineStr">
@@ -14774,7 +16728,11 @@
         <v>16.35</v>
       </c>
       <c r="H452" s="10" t="n"/>
-      <c r="I452" s="10" t="n"/>
+      <c r="I452" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="8" t="inlineStr">
@@ -14805,7 +16763,11 @@
         <v>17.77</v>
       </c>
       <c r="H453" s="10" t="n"/>
-      <c r="I453" s="10" t="n"/>
+      <c r="I453" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="8" t="inlineStr">
@@ -14836,7 +16798,11 @@
         <v>25.71</v>
       </c>
       <c r="H454" s="10" t="n"/>
-      <c r="I454" s="10" t="n"/>
+      <c r="I454" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="8" t="inlineStr">
@@ -14867,7 +16833,11 @@
         <v>16.06</v>
       </c>
       <c r="H455" s="10" t="n"/>
-      <c r="I455" s="10" t="n"/>
+      <c r="I455" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="8" t="inlineStr">
@@ -14898,7 +16868,11 @@
         <v>22.45</v>
       </c>
       <c r="H456" s="10" t="n"/>
-      <c r="I456" s="10" t="n"/>
+      <c r="I456" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="8" t="inlineStr">
@@ -14929,7 +16903,11 @@
         <v>23.36</v>
       </c>
       <c r="H457" s="10" t="n"/>
-      <c r="I457" s="10" t="n"/>
+      <c r="I457" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="8" t="inlineStr">
@@ -14960,7 +16938,11 @@
         <v>9.73</v>
       </c>
       <c r="H458" s="10" t="n"/>
-      <c r="I458" s="10" t="n"/>
+      <c r="I458" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="8" t="inlineStr">
@@ -14991,7 +16973,11 @@
         <v>14.22</v>
       </c>
       <c r="H459" s="10" t="n"/>
-      <c r="I459" s="10" t="n"/>
+      <c r="I459" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="8" t="inlineStr">
@@ -15022,7 +17008,11 @@
         <v>15.01</v>
       </c>
       <c r="H460" s="10" t="n"/>
-      <c r="I460" s="10" t="n"/>
+      <c r="I460" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="8" t="inlineStr">
@@ -15053,7 +17043,11 @@
         <v>21.24</v>
       </c>
       <c r="H461" s="10" t="n"/>
-      <c r="I461" s="10" t="n"/>
+      <c r="I461" s="10" t="inlineStr">
+        <is>
+          <t>Vendor: A.K. TRADING PVT LTD · lead 1 Day</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15682,7 +17676,11 @@
       <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="10" t="n"/>
-      <c r="K5" s="10" t="n"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>No per-click rate in uploaded data — pending NKK sir</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -15711,7 +17709,11 @@
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>No per-click rate in uploaded data — pending NKK sir</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -15740,7 +17742,11 @@
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>No per-click rate in uploaded data — pending NKK sir</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -15769,7 +17775,11 @@
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>No per-click rate in uploaded data — pending NKK sir</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -15900,7 +17910,11 @@
         <v>550</v>
       </c>
       <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="n"/>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Src: NABAMUDRAN PVT LTD · max B1 Format · 9000 iph · 4 COL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -15928,7 +17942,11 @@
         <v>450</v>
       </c>
       <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Src: NABAMUDRAN PVT LTD · max B2 Format · 8000 iph · 5 COL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -15956,7 +17974,11 @@
         <v>550</v>
       </c>
       <c r="I7" s="10" t="n"/>
-      <c r="J7" s="10" t="n"/>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Src: NABAMUDRAN PVT LTD · max B1 Format · 7000 iph · 2 COL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -15988,7 +18010,11 @@
         <v>550</v>
       </c>
       <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Src: NABAMUDRAN PVT LTD · max B1 Format · 7000 iph · 4 COL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -16016,7 +18042,11 @@
         <v>400</v>
       </c>
       <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Src: BALAJI PRINTING SOLUTION · max B1 Format · 15000 iph · 4 COL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -16044,7 +18074,11 @@
         <v>400</v>
       </c>
       <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Src: BALAJI PRINTING SOLUTION · max B2+ Format · 13000 iph · 4 COL</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -16072,7 +18106,11 @@
         <v>400</v>
       </c>
       <c r="I11" s="10" t="n"/>
-      <c r="J11" s="10" t="n"/>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Src: FLORENCE OFFSET PVT LTD · max B2+ Format · 13000 iph · 4 COL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -16100,7 +18138,11 @@
         <v>400</v>
       </c>
       <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Src: FLORENCE OFFSET PVT LTD · max B2+ Format · 13000 iph · SINGLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -17065,7 +19107,9 @@
       <c r="D6" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="E6" s="10" t="n"/>
+      <c r="E6" s="10" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -17084,7 +19128,9 @@
       <c r="D7" s="9" t="n">
         <v>800</v>
       </c>
-      <c r="E7" s="10" t="n"/>
+      <c r="E7" s="10" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -17198,7 +19244,9 @@
       <c r="D13" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="E13" s="10" t="n"/>
+      <c r="E13" s="10" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -17255,7 +19303,9 @@
       <c r="D16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="10" t="n"/>
+      <c r="E16" s="10" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -17274,7 +19324,9 @@
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="10" t="n"/>
+      <c r="E17" s="10" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -17388,7 +19440,9 @@
       <c r="D23" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="E23" s="10" t="n"/>
+      <c r="E23" s="10" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -17690,10 +19744,12 @@
       <c r="C5" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="D5" s="10" t="n"/>
+      <c r="D5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>placeholder — confirm; or give Rs/parent-board + size</t>
+          <t>Board cost included in Case-making Rs 95/book (combined)</t>
         </is>
       </c>
     </row>
@@ -17716,7 +19772,7 @@
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>size boards are cut from — confirm</t>
+          <t>Size boards are cut from; material cost included in Rs 95/book</t>
         </is>
       </c>
     </row>
@@ -17737,7 +19793,7 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>Default spec (2.5 mm) — not a separate charge</t>
         </is>
       </c>
     </row>
@@ -17885,10 +19941,12 @@
       <c r="C14" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="10" t="n"/>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — confirm (or Rs/metre)</t>
+          <t>Included in Case-making Rs 95/book (combined rate)</t>
         </is>
       </c>
     </row>
@@ -17906,10 +19964,12 @@
       <c r="C15" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="D15" s="10" t="n"/>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — confirm (or Rs/metre)</t>
+          <t>Included in Case-making Rs 95/book (combined rate)</t>
         </is>
       </c>
     </row>
@@ -17927,10 +19987,12 @@
       <c r="C16" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="D16" s="10" t="n"/>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — confirm (or Rs/metre)</t>
+          <t>Included in Case-making Rs 95/book (combined rate)</t>
         </is>
       </c>
     </row>
@@ -17948,10 +20010,12 @@
       <c r="C17" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="D17" s="10" t="n"/>
+      <c r="D17" s="10" t="n">
+        <v>95</v>
+      </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>real (POST_PRESS) — confirm still current</t>
+          <t>Confirmed from POST_PRESS (N.C. Paper Binding Works) — Rs 95/book</t>
         </is>
       </c>
     </row>
@@ -17969,10 +20033,12 @@
       <c r="C18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="10" t="n"/>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Included in Case-making Rs 95/book (combined rate)</t>
         </is>
       </c>
     </row>
@@ -17990,10 +20056,12 @@
       <c r="C19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="10" t="n"/>
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>Included in Case-making Rs 95/book (combined rate)</t>
         </is>
       </c>
     </row>
@@ -18023,7 +20091,15 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PENDING: rexine/cloth/velvet, headband, ribbon, board grade+size, spine-board reduction.</t>
+          <t>Board, rexine/cloth/velvet, headband &amp; ribbon are all bundled into Case-making Rs 95/book.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Combined rate confirmed (N.C. Paper Binding Works)</t>
         </is>
       </c>
     </row>
@@ -18106,7 +20182,7 @@
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>per design — confirm</t>
+          <t>Vendor gives ONE all-inclusive rate (forme + die-cutting + gluing); not in uploaded data — pending NKK sir</t>
         </is>
       </c>
     </row>
@@ -18127,7 +20203,7 @@
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>running — confirm</t>
+          <t>Covered by the all-inclusive die rate above</t>
         </is>
       </c>
     </row>
@@ -18148,7 +20224,7 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>confirm by product type</t>
+          <t>Covered by the all-inclusive die rate above</t>
         </is>
       </c>
     </row>

--- a/db/MASTER_DATABASE_2026.xlsx
+++ b/db/MASTER_DATABASE_2026.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Machines (Offset)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Digital press rate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Press rates (Offset)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binding" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coating &amp; Embellishment" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hard-case materials rate" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dieline &amp; converting" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire-O diameters" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="00 README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Paper" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Machines (Offset)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Digital press rate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Press rates (Offset)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Binding" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Coating &amp; Embellishment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Hard-case materials rate" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dieline &amp; converting" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Wire-O diameters" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,12 @@
       <b val="1"/>
       <color rgb="0013314F"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0013314F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -129,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +163,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17562,14 +17578,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -17785,6 +17801,119 @@
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>PENDING: NKK sir to provide per-click rates per press (and per colour if it varies).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>NKK sir digital rate card (2026-06-27) — FLAT ₹/sheet, printed BOTH SIDES, up to ~20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Paper class</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Sheet size</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>4-colour both-side ₹/sheet</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Single-colour both-side ₹/sheet</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Art Paper / Maplitho (standard)</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>12 x 18</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>standard = art/maplitho/coated/uncoated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Art Paper / Maplitho (standard)</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>13 x 19</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Special Paper</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>12 x 18</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Special Paper</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>13 x 19</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Single-colour both-side rates PENDING sir. Wired into the app: digital printing = ₹/sheet × printed sheets.</t>
         </is>
       </c>
     </row>
